--- a/Result/Bearing_Result_30/Result_Bearing_30.xlsx
+++ b/Result/Bearing_Result_30/Result_Bearing_30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\imb_project\Result\Bearing_Result_30\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF74A529-39F6-4E50-BB91-5859F738A6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465027D3-7267-4ED7-8F69-EAC4B975D456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="54">
   <si>
     <t>Model</t>
   </si>
@@ -179,6 +179,9 @@
   </si>
   <si>
     <t>IR30_SEU</t>
+  </si>
+  <si>
+    <t>setting an array element with a sequence.</t>
   </si>
 </sst>
 </file>
@@ -525,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z126"/>
+  <dimension ref="A1:AA136"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.15">
@@ -7890,10 +7893,10 @@
     </row>
     <row r="93" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A93" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B93" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C93" t="s">
         <v>28</v>
@@ -7902,78 +7905,78 @@
         <v>29</v>
       </c>
       <c r="E93">
-        <v>0.99220779220779209</v>
+        <v>0.97846639128392954</v>
       </c>
       <c r="F93">
-        <v>6.3623110202160492E-3</v>
+        <v>2.8895794528896769E-3</v>
       </c>
       <c r="G93">
-        <v>0.98193466353677616</v>
+        <v>0.9289299957295466</v>
       </c>
       <c r="H93">
-        <v>3.2671446853855382E-2</v>
+        <v>2.1353103843169619E-2</v>
       </c>
       <c r="I93">
-        <v>0.95761904761904759</v>
+        <v>0.80850565394616891</v>
       </c>
       <c r="J93">
-        <v>5.2156445283210201E-2</v>
+        <v>2.1563684375766699E-2</v>
       </c>
       <c r="K93">
-        <v>0.96226936082438908</v>
+        <v>0.85193584420438384</v>
       </c>
       <c r="L93">
-        <v>3.3119209120691308E-2</v>
+        <v>2.140022740951477E-2</v>
       </c>
       <c r="M93">
-        <v>0.94818153932348148</v>
+        <v>0.76570627817824033</v>
       </c>
       <c r="N93">
-        <v>6.5105534847637023E-2</v>
+        <v>3.3323332779917968E-2</v>
       </c>
       <c r="O93">
-        <v>0.99966321739963582</v>
+        <v>0.97871975781660514</v>
       </c>
       <c r="P93">
-        <v>4.6277170066955119E-4</v>
+        <v>3.3974192944847409E-3</v>
       </c>
       <c r="Q93">
-        <v>0.95247809506514669</v>
+        <v>0.8046863884099309</v>
       </c>
       <c r="R93">
-        <v>3.9437041540834682E-2</v>
+        <v>2.8002451970750089E-2</v>
       </c>
       <c r="S93">
-        <v>0.99997024006322754</v>
+        <v>0.89131976747678154</v>
       </c>
       <c r="T93">
-        <v>3.9506541174216609E-5</v>
+        <v>1.8073782103726541E-2</v>
       </c>
       <c r="U93">
-        <v>0.95353287981859403</v>
+        <v>0.80728038939269342</v>
       </c>
       <c r="V93">
-        <v>5.7011300444979457E-2</v>
+        <v>1.706771278361453E-2</v>
       </c>
       <c r="W93">
-        <v>0.95036142090045439</v>
+        <v>0.79722061832210611</v>
       </c>
       <c r="X93">
-        <v>4.1246807644686967E-2</v>
+        <v>2.8968421179208531E-2</v>
       </c>
       <c r="Y93">
-        <v>7.2542199999999983</v>
+        <v>1.171288679999998</v>
       </c>
       <c r="Z93">
-        <v>2.0586861318215108</v>
+        <v>0.55114289795600313</v>
       </c>
     </row>
     <row r="94" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A94" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B94" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C94" t="s">
         <v>28</v>
@@ -7982,78 +7985,78 @@
         <v>29</v>
       </c>
       <c r="E94">
-        <v>0.9974025974025974</v>
+        <v>0.97242235653641984</v>
       </c>
       <c r="F94">
-        <v>5.1948051948051974E-3</v>
+        <v>1.0311786577848459E-3</v>
       </c>
       <c r="G94">
-        <v>0.98333333333333317</v>
+        <v>0.85656847147631476</v>
       </c>
       <c r="H94">
-        <v>3.3333333333333347E-2</v>
+        <v>6.9502942664859974E-3</v>
       </c>
       <c r="I94">
-        <v>0.99929577464788721</v>
+        <v>0.81131424790913675</v>
       </c>
       <c r="J94">
-        <v>1.40845070422535E-3</v>
+        <v>1.7177862572039161E-2</v>
       </c>
       <c r="K94">
-        <v>0.989645390070922</v>
+        <v>0.83217921553970309</v>
       </c>
       <c r="L94">
-        <v>2.070921985815604E-2</v>
+        <v>1.050816197835623E-2</v>
       </c>
       <c r="M94">
-        <v>0.99929202428944564</v>
+        <v>0.77809928558198505</v>
       </c>
       <c r="N94">
-        <v>1.4159514211089521E-3</v>
+        <v>2.2964276247991341E-2</v>
       </c>
       <c r="O94">
-        <v>1</v>
+        <v>0.97426203612512319</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.6053038886185102E-3</v>
       </c>
       <c r="Q94">
-        <v>0.98437728326295537</v>
+        <v>0.75780508510142341</v>
       </c>
       <c r="R94">
-        <v>3.1245433474089219E-2</v>
+        <v>1.163852396455127E-2</v>
       </c>
       <c r="S94">
-        <v>1</v>
+        <v>0.85483140452105011</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>1.2716303501063571E-2</v>
       </c>
       <c r="U94">
-        <v>0.9992819546386299</v>
+        <v>0.80266167945515698</v>
       </c>
       <c r="V94">
-        <v>1.436090722740202E-3</v>
+        <v>1.6345709970723252E-2</v>
       </c>
       <c r="W94">
-        <v>0.98370370370370375</v>
+        <v>0.75640672206387993</v>
       </c>
       <c r="X94">
-        <v>3.2592592592592597E-2</v>
+        <v>1.2362690998580761E-2</v>
       </c>
       <c r="Y94">
-        <v>94.111120780000007</v>
+        <v>1.994611000000168</v>
       </c>
       <c r="Z94">
-        <v>10.542140765884829</v>
+        <v>4.6684247472263032E-2</v>
       </c>
     </row>
     <row r="95" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A95" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B95" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C95" t="s">
         <v>28</v>
@@ -8062,78 +8065,78 @@
         <v>29</v>
       </c>
       <c r="E95">
-        <v>0.9948051948051948</v>
+        <v>0.96681875418285412</v>
       </c>
       <c r="F95">
-        <v>1.038961038961039E-2</v>
+        <v>1.6131244875735411E-3</v>
       </c>
       <c r="G95">
-        <v>0.97428571428571442</v>
+        <v>0.81648854458308406</v>
       </c>
       <c r="H95">
-        <v>5.1428571428571421E-2</v>
+        <v>8.8045780361256012E-3</v>
       </c>
       <c r="I95">
-        <v>0.97428571428571442</v>
+        <v>0.8456765487580078</v>
       </c>
       <c r="J95">
-        <v>5.1428571428571421E-2</v>
+        <v>2.030119392327227E-2</v>
       </c>
       <c r="K95">
-        <v>0.97428571428571442</v>
+        <v>0.8294914857777359</v>
       </c>
       <c r="L95">
-        <v>5.1428571428571421E-2</v>
+        <v>1.2438779736553241E-2</v>
       </c>
       <c r="M95">
-        <v>0.96757539795775072</v>
+        <v>0.82405366509771005</v>
       </c>
       <c r="N95">
-        <v>6.4849204084498402E-2</v>
+        <v>2.8557692319679969E-2</v>
       </c>
       <c r="O95">
-        <v>0.99956462585034012</v>
+        <v>0.97343339764557546</v>
       </c>
       <c r="P95">
-        <v>8.7074829931972349E-4</v>
+        <v>3.6410605667229362E-3</v>
       </c>
       <c r="Q95">
-        <v>0.9695652173913043</v>
+        <v>0.73382722836558922</v>
       </c>
       <c r="R95">
-        <v>6.0869565217391307E-2</v>
+        <v>1.6881589182632249E-2</v>
       </c>
       <c r="S95">
-        <v>0.99165660630449359</v>
+        <v>0.85048332398464499</v>
       </c>
       <c r="T95">
-        <v>1.668678739101272E-2</v>
+        <v>1.7112954418065651E-2</v>
       </c>
       <c r="U95">
-        <v>0.97137074829931969</v>
+        <v>0.8341278052017298</v>
       </c>
       <c r="V95">
-        <v>5.7258503401360537E-2</v>
+        <v>1.7457660861001478E-2</v>
       </c>
       <c r="W95">
-        <v>0.9695652173913043</v>
+        <v>0.73280321202325283</v>
       </c>
       <c r="X95">
-        <v>6.0869565217391307E-2</v>
+        <v>1.6334550198917622E-2</v>
       </c>
       <c r="Y95">
-        <v>0.13197437999999689</v>
+        <v>1902.9494730399999</v>
       </c>
       <c r="Z95">
-        <v>7.7334524710393881E-3</v>
+        <v>64.315481648001736</v>
       </c>
     </row>
     <row r="96" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A96" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B96" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C96" t="s">
         <v>28</v>
@@ -8142,78 +8145,78 @@
         <v>29</v>
       </c>
       <c r="E96">
-        <v>1</v>
+        <v>0.97326300504081475</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>2.9144861497725689E-3</v>
       </c>
       <c r="G96">
-        <v>1</v>
+        <v>0.84716580523573926</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>1.6791358248593079E-2</v>
       </c>
       <c r="I96">
-        <v>1</v>
+        <v>0.85085955676344904</v>
       </c>
       <c r="J96">
-        <v>0</v>
+        <v>2.2645943020202241E-2</v>
       </c>
       <c r="K96">
-        <v>1</v>
+        <v>0.84837173182800529</v>
       </c>
       <c r="L96">
-        <v>0</v>
+        <v>1.833947206068819E-2</v>
       </c>
       <c r="M96">
-        <v>1</v>
+        <v>0.82760358080897911</v>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>3.0848690239032011E-2</v>
       </c>
       <c r="O96">
-        <v>1</v>
+        <v>0.97920769455860357</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>3.599831825986873E-3</v>
       </c>
       <c r="Q96">
-        <v>1</v>
+        <v>0.77527166062724862</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.5493153153588698E-2</v>
       </c>
       <c r="S96">
-        <v>1</v>
+        <v>0.87603474506068491</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>2.138496369541203E-2</v>
       </c>
       <c r="U96">
-        <v>1</v>
+        <v>0.84129581358685712</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>2.029451404175318E-2</v>
       </c>
       <c r="W96">
-        <v>1</v>
+        <v>0.77508604280220728</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>2.53535457365744E-2</v>
       </c>
       <c r="Y96">
-        <v>8.6434992800000376</v>
+        <v>9.9399976000015151</v>
       </c>
       <c r="Z96">
-        <v>1.2848892600363531</v>
-      </c>
-    </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.15">
+        <v>0.67437799507452567</v>
+      </c>
+    </row>
+    <row r="97" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A97" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B97" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C97" t="s">
         <v>28</v>
@@ -8222,78 +8225,78 @@
         <v>29</v>
       </c>
       <c r="E97">
-        <v>0.99220779220779209</v>
+        <v>0.97754569475071751</v>
       </c>
       <c r="F97">
-        <v>6.3623110202160492E-3</v>
+        <v>1.621982636937623E-3</v>
       </c>
       <c r="G97">
-        <v>0.98193466353677616</v>
+        <v>0.89600583964587754</v>
       </c>
       <c r="H97">
-        <v>3.2671446853855382E-2</v>
+        <v>9.2500990146153934E-3</v>
       </c>
       <c r="I97">
-        <v>0.93333333333333324</v>
+        <v>0.8321393062833714</v>
       </c>
       <c r="J97">
-        <v>5.6519416526043913E-2</v>
+        <v>1.36680895372646E-2</v>
       </c>
       <c r="K97">
-        <v>0.94596240638793816</v>
+        <v>0.85856495855769643</v>
       </c>
       <c r="L97">
-        <v>5.1179673602798889E-2</v>
+        <v>1.1593379741357331E-2</v>
       </c>
       <c r="M97">
-        <v>0.9170789668234548</v>
+        <v>0.8025102614880828</v>
       </c>
       <c r="N97">
-        <v>7.1471653613085939E-2</v>
+        <v>2.106498304796238E-2</v>
       </c>
       <c r="O97">
-        <v>1</v>
+        <v>0.97972566925125837</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>2.5794085420726299E-3</v>
       </c>
       <c r="Q97">
-        <v>0.95117122923097563</v>
+        <v>0.80085331248578484</v>
       </c>
       <c r="R97">
-        <v>4.0215724123578378E-2</v>
+        <v>1.5420606670635341E-2</v>
       </c>
       <c r="S97">
-        <v>1</v>
+        <v>0.88581034089782773</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>2.1235087889519041E-2</v>
       </c>
       <c r="U97">
-        <v>0.92334920634920636</v>
+        <v>0.82502332117729116</v>
       </c>
       <c r="V97">
-        <v>6.5655559268328431E-2</v>
+        <v>1.0583567708870841E-2</v>
       </c>
       <c r="W97">
-        <v>0.94940328885536585</v>
+        <v>0.79835034722239651</v>
       </c>
       <c r="X97">
-        <v>4.179082572384106E-2</v>
+        <v>1.5904306188633619E-2</v>
       </c>
       <c r="Y97">
-        <v>0.1161875799999962</v>
+        <v>346.76677463999948</v>
       </c>
       <c r="Z97">
-        <v>1.6395132697283151E-2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.15">
+        <v>22.0890299201468</v>
+      </c>
+    </row>
+    <row r="98" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A98" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B98" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C98" t="s">
         <v>28</v>
@@ -8302,158 +8305,158 @@
         <v>29</v>
       </c>
       <c r="E98">
-        <v>0.9974025974025974</v>
+        <v>0.95260959618204866</v>
       </c>
       <c r="F98">
-        <v>5.1948051948051974E-3</v>
+        <v>3.7264355814691551E-3</v>
       </c>
       <c r="G98">
-        <v>0.99929577464788721</v>
+        <v>0.76029142317951059</v>
       </c>
       <c r="H98">
-        <v>1.40845070422535E-3</v>
+        <v>1.1891465488984419E-2</v>
       </c>
       <c r="I98">
-        <v>0.98333333333333317</v>
+        <v>0.86871688807991876</v>
       </c>
       <c r="J98">
-        <v>3.3333333333333347E-2</v>
+        <v>1.52522388366948E-2</v>
       </c>
       <c r="K98">
-        <v>0.989645390070922</v>
+        <v>0.80074872763726535</v>
       </c>
       <c r="L98">
-        <v>2.070921985815604E-2</v>
+        <v>1.192156464975451E-2</v>
       </c>
       <c r="M98">
-        <v>0.98072040072196887</v>
+        <v>0.85683655524479774</v>
       </c>
       <c r="N98">
-        <v>3.8559198556062102E-2</v>
+        <v>1.9684271638823449E-2</v>
       </c>
       <c r="O98">
-        <v>1</v>
+        <v>0.9729775884552041</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.5743186849025369E-3</v>
       </c>
       <c r="Q98">
-        <v>0.98437728326295537</v>
+        <v>0.67890542646705554</v>
       </c>
       <c r="R98">
-        <v>3.1245433474089219E-2</v>
+        <v>2.1941429064967561E-2</v>
       </c>
       <c r="S98">
-        <v>1</v>
+        <v>0.83424863672814653</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>2.2694404871541979E-2</v>
       </c>
       <c r="U98">
-        <v>0.9813492063492063</v>
+        <v>0.8528269781407648</v>
       </c>
       <c r="V98">
-        <v>3.7301587301587308E-2</v>
+        <v>1.4011858330928729E-2</v>
       </c>
       <c r="W98">
-        <v>0.98370370370370375</v>
+        <v>0.66722880869377121</v>
       </c>
       <c r="X98">
-        <v>3.2592592592592597E-2</v>
+        <v>2.2539522296660858E-2</v>
       </c>
       <c r="Y98">
-        <v>0.35636941999998728</v>
+        <v>0.41782426000136191</v>
       </c>
       <c r="Z98">
-        <v>1.7535286886670109E-2</v>
-      </c>
-    </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.15">
+        <v>7.5382565346401188E-3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A99" t="s">
+        <v>43</v>
+      </c>
+      <c r="B99" t="s">
+        <v>50</v>
+      </c>
+      <c r="C99" t="s">
+        <v>28</v>
+      </c>
+      <c r="D99" t="s">
+        <v>29</v>
+      </c>
+      <c r="E99">
+        <v>0.97574462211354029</v>
+      </c>
+      <c r="F99">
+        <v>2.1480070431749449E-3</v>
+      </c>
+      <c r="G99">
+        <v>0.86506570757147505</v>
+      </c>
+      <c r="H99">
+        <v>1.0228192053250439E-2</v>
+      </c>
+      <c r="I99">
+        <v>0.86248294412490156</v>
+      </c>
+      <c r="J99">
+        <v>1.5513428756997761E-2</v>
+      </c>
+      <c r="K99">
+        <v>0.86347353575889441</v>
+      </c>
+      <c r="L99">
+        <v>1.2796079097424881E-2</v>
+      </c>
+      <c r="M99">
+        <v>0.84511198310003677</v>
+      </c>
+      <c r="N99">
+        <v>2.0079249497534708E-2</v>
+      </c>
+      <c r="O99">
+        <v>0.98209209556413835</v>
+      </c>
+      <c r="P99">
+        <v>1.1542280633612379E-3</v>
+      </c>
+      <c r="Q99">
+        <v>0.79527040078804756</v>
+      </c>
+      <c r="R99">
+        <v>1.8890435971144291E-2</v>
+      </c>
+      <c r="S99">
+        <v>0.88673054324801459</v>
+      </c>
+      <c r="T99">
+        <v>1.6255875676182651E-2</v>
+      </c>
+      <c r="U99">
+        <v>0.85065633128055518</v>
+      </c>
+      <c r="V99">
+        <v>1.448610082052445E-2</v>
+      </c>
+      <c r="W99">
+        <v>0.7952028118955462</v>
+      </c>
+      <c r="X99">
+        <v>1.892762048145066E-2</v>
+      </c>
+      <c r="Y99">
+        <v>140.23765235999889</v>
+      </c>
+      <c r="Z99">
+        <v>15.256513502548589</v>
+      </c>
+    </row>
+    <row r="100" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A100" t="s">
         <v>35</v>
       </c>
-      <c r="B99" t="s">
-        <v>52</v>
-      </c>
-      <c r="C99" t="s">
-        <v>28</v>
-      </c>
-      <c r="D99" t="s">
-        <v>29</v>
-      </c>
-      <c r="E99">
-        <v>0.9974025974025974</v>
-      </c>
-      <c r="F99">
-        <v>5.1948051948051974E-3</v>
-      </c>
-      <c r="G99">
-        <v>0.98333333333333317</v>
-      </c>
-      <c r="H99">
-        <v>3.3333333333333347E-2</v>
-      </c>
-      <c r="I99">
-        <v>0.99929577464788721</v>
-      </c>
-      <c r="J99">
-        <v>1.40845070422535E-3</v>
-      </c>
-      <c r="K99">
-        <v>0.989645390070922</v>
-      </c>
-      <c r="L99">
-        <v>2.070921985815604E-2</v>
-      </c>
-      <c r="M99">
-        <v>0.99929202428944564</v>
-      </c>
-      <c r="N99">
-        <v>1.4159514211089521E-3</v>
-      </c>
-      <c r="O99">
-        <v>1</v>
-      </c>
-      <c r="P99">
-        <v>0</v>
-      </c>
-      <c r="Q99">
-        <v>0.98437728326295537</v>
-      </c>
-      <c r="R99">
-        <v>3.1245433474089219E-2</v>
-      </c>
-      <c r="S99">
-        <v>1</v>
-      </c>
-      <c r="T99">
-        <v>0</v>
-      </c>
-      <c r="U99">
-        <v>0.9992819546386299</v>
-      </c>
-      <c r="V99">
-        <v>1.436090722740202E-3</v>
-      </c>
-      <c r="W99">
-        <v>0.98370370370370375</v>
-      </c>
-      <c r="X99">
-        <v>3.2592592592592597E-2</v>
-      </c>
-      <c r="Y99">
-        <v>3.1092247600000058</v>
-      </c>
-      <c r="Z99">
-        <v>0.1581237248902693</v>
-      </c>
-    </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.15">
-      <c r="A100" t="s">
-        <v>36</v>
-      </c>
       <c r="B100" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C100" t="s">
         <v>28</v>
@@ -8461,79 +8464,16 @@
       <c r="D100" t="s">
         <v>29</v>
       </c>
-      <c r="E100">
-        <v>0.9974025974025974</v>
-      </c>
-      <c r="F100">
-        <v>5.1948051948051974E-3</v>
-      </c>
-      <c r="G100">
-        <v>0.99929577464788721</v>
-      </c>
-      <c r="H100">
-        <v>1.40845070422535E-3</v>
-      </c>
-      <c r="I100">
-        <v>0.98333333333333317</v>
-      </c>
-      <c r="J100">
-        <v>3.3333333333333347E-2</v>
-      </c>
-      <c r="K100">
-        <v>0.989645390070922</v>
-      </c>
-      <c r="L100">
-        <v>2.070921985815604E-2</v>
-      </c>
-      <c r="M100">
-        <v>0.98072040072196887</v>
-      </c>
-      <c r="N100">
-        <v>3.8559198556062102E-2</v>
-      </c>
-      <c r="O100">
-        <v>1</v>
-      </c>
-      <c r="P100">
-        <v>0</v>
-      </c>
-      <c r="Q100">
-        <v>0.98437728326295537</v>
-      </c>
-      <c r="R100">
-        <v>3.1245433474089219E-2</v>
-      </c>
-      <c r="S100">
-        <v>1</v>
-      </c>
-      <c r="T100">
-        <v>0</v>
-      </c>
-      <c r="U100">
-        <v>0.9813492063492063</v>
-      </c>
-      <c r="V100">
-        <v>3.7301587301587308E-2</v>
-      </c>
-      <c r="W100">
-        <v>0.98370370370370375</v>
-      </c>
-      <c r="X100">
-        <v>3.2592592592592597E-2</v>
-      </c>
-      <c r="Y100">
-        <v>0.1245722999999998</v>
-      </c>
-      <c r="Z100">
-        <v>6.1068052580646589E-3</v>
-      </c>
-    </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA100" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="101" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A101" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B101" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C101" t="s">
         <v>28</v>
@@ -8542,78 +8482,78 @@
         <v>29</v>
       </c>
       <c r="E101">
-        <v>1</v>
+        <v>0.96982065139804463</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>2.3797657303360458E-3</v>
       </c>
       <c r="G101">
-        <v>1</v>
+        <v>0.8268282166411034</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>1.4271374494981909E-2</v>
       </c>
       <c r="I101">
-        <v>1</v>
+        <v>0.84261262098963863</v>
       </c>
       <c r="J101">
-        <v>0</v>
+        <v>1.686788184813787E-2</v>
       </c>
       <c r="K101">
-        <v>1</v>
+        <v>0.83437909051837345</v>
       </c>
       <c r="L101">
-        <v>0</v>
+        <v>1.3467676443358591E-2</v>
       </c>
       <c r="M101">
-        <v>1</v>
+        <v>0.81949427342937375</v>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.3752715519923102E-2</v>
       </c>
       <c r="O101">
-        <v>1</v>
+        <v>0.97509824578882731</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>1.6305595224368711E-3</v>
       </c>
       <c r="Q101">
-        <v>1</v>
+        <v>0.7504810020257271</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>1.9787450172094771E-2</v>
       </c>
       <c r="S101">
-        <v>1</v>
+        <v>0.85439792833854056</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>1.2777973209196471E-2</v>
       </c>
       <c r="U101">
-        <v>1</v>
+        <v>0.83188269374007773</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.4451265703522649E-2</v>
       </c>
       <c r="W101">
-        <v>1</v>
+        <v>0.7502298230437463</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.9765542704603449E-2</v>
       </c>
       <c r="Y101">
-        <v>25.28726451999999</v>
+        <v>2378.0563743000012</v>
       </c>
       <c r="Z101">
-        <v>0.32369396922137461</v>
-      </c>
-    </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.15">
+        <v>3.5842976778435891</v>
+      </c>
+    </row>
+    <row r="102" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A102" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B102" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C102" t="s">
         <v>28</v>
@@ -8622,75 +8562,75 @@
         <v>29</v>
       </c>
       <c r="E102">
-        <v>0.9974025974025974</v>
+        <v>0.94696599384770974</v>
       </c>
       <c r="F102">
-        <v>5.1948051948051974E-3</v>
+        <v>1.0316444497425129E-3</v>
       </c>
       <c r="G102">
-        <v>0.98333333333333339</v>
+        <v>0.75707923714045378</v>
       </c>
       <c r="H102">
-        <v>3.3333333333333347E-2</v>
+        <v>4.2900449184031216E-3</v>
       </c>
       <c r="I102">
-        <v>0.99928571428571433</v>
+        <v>0.92950466030687351</v>
       </c>
       <c r="J102">
-        <v>1.428571428571424E-3</v>
+        <v>1.089024854948804E-2</v>
       </c>
       <c r="K102">
-        <v>0.98964028776978419</v>
+        <v>0.80999057941260111</v>
       </c>
       <c r="L102">
-        <v>2.0719424460431669E-2</v>
+        <v>2.8864291137325289E-3</v>
       </c>
       <c r="M102">
-        <v>0.99928185555076965</v>
+        <v>0.92817436011453724</v>
       </c>
       <c r="N102">
-        <v>1.436288898460614E-3</v>
+        <v>1.184862403254768E-2</v>
       </c>
       <c r="O102">
-        <v>0.99994897959183682</v>
+        <v>0.98592519505439902</v>
       </c>
       <c r="P102">
-        <v>1.0204081632654289E-4</v>
+        <v>1.8826688308996259E-3</v>
       </c>
       <c r="Q102">
-        <v>0.98627233712647233</v>
+        <v>0.69328374469202192</v>
       </c>
       <c r="R102">
-        <v>2.7455325747055288E-2</v>
+        <v>5.2671271330355226E-3</v>
       </c>
       <c r="S102">
-        <v>0.99998993963782701</v>
+        <v>0.91274056111206592</v>
       </c>
       <c r="T102">
-        <v>2.0120724346073259E-5</v>
+        <v>1.5720544166087369E-2</v>
       </c>
       <c r="U102">
-        <v>0.99926700680272107</v>
+        <v>0.91676437661227195</v>
       </c>
       <c r="V102">
-        <v>1.465986394557817E-3</v>
+        <v>1.2402377782175841E-2</v>
       </c>
       <c r="W102">
-        <v>0.98574074074074081</v>
+        <v>0.6653191628483599</v>
       </c>
       <c r="X102">
-        <v>2.8518518518518519E-2</v>
+        <v>3.8317390289135411E-3</v>
       </c>
       <c r="Y102">
-        <v>9.7567619999995261E-2</v>
+        <v>9.7148690400004849</v>
       </c>
       <c r="Z102">
-        <v>7.6744903792753272E-3</v>
-      </c>
-    </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.15">
+        <v>0.1072506866876984</v>
+      </c>
+    </row>
+    <row r="103" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A103" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B103" t="s">
         <v>52</v>
@@ -8702,75 +8642,75 @@
         <v>29</v>
       </c>
       <c r="E103">
-        <v>1</v>
+        <v>0.99220779220779209</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>6.3623110202160492E-3</v>
       </c>
       <c r="G103">
-        <v>1</v>
+        <v>0.98193466353677616</v>
       </c>
       <c r="H103">
-        <v>0</v>
+        <v>3.2671446853855382E-2</v>
       </c>
       <c r="I103">
-        <v>1</v>
+        <v>0.95761904761904759</v>
       </c>
       <c r="J103">
-        <v>0</v>
+        <v>5.2156445283210201E-2</v>
       </c>
       <c r="K103">
-        <v>1</v>
+        <v>0.96226936082438908</v>
       </c>
       <c r="L103">
-        <v>0</v>
+        <v>3.3119209120691308E-2</v>
       </c>
       <c r="M103">
-        <v>1</v>
+        <v>0.94818153932348148</v>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>6.5105534847637023E-2</v>
       </c>
       <c r="O103">
-        <v>1</v>
+        <v>0.99966321739963582</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>4.6277170066955119E-4</v>
       </c>
       <c r="Q103">
-        <v>1</v>
+        <v>0.95247809506514669</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>3.9437041540834682E-2</v>
       </c>
       <c r="S103">
-        <v>1</v>
+        <v>0.99997024006322754</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>3.9506541174216609E-5</v>
       </c>
       <c r="U103">
-        <v>1</v>
+        <v>0.95353287981859403</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>5.7011300444979457E-2</v>
       </c>
       <c r="W103">
-        <v>1</v>
+        <v>0.95036142090045439</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>4.1246807644686967E-2</v>
       </c>
       <c r="Y103">
-        <v>11.01138922</v>
+        <v>7.2542199999999983</v>
       </c>
       <c r="Z103">
-        <v>0.1120388191995029</v>
-      </c>
-    </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.15">
+        <v>2.0586861318215108</v>
+      </c>
+    </row>
+    <row r="104" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A104" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B104" t="s">
         <v>52</v>
@@ -8788,69 +8728,69 @@
         <v>5.1948051948051974E-3</v>
       </c>
       <c r="G104">
-        <v>0.99930555555555556</v>
+        <v>0.98333333333333317</v>
       </c>
       <c r="H104">
-        <v>1.388888888888884E-3</v>
+        <v>3.3333333333333347E-2</v>
       </c>
       <c r="I104">
-        <v>0.97499999999999998</v>
+        <v>0.99929577464788721</v>
       </c>
       <c r="J104">
-        <v>0.05</v>
+        <v>1.40845070422535E-3</v>
       </c>
       <c r="K104">
-        <v>0.98298368298368288</v>
+        <v>0.989645390070922</v>
       </c>
       <c r="L104">
-        <v>3.4032634032634047E-2</v>
+        <v>2.070921985815604E-2</v>
       </c>
       <c r="M104">
-        <v>0.96817928305074297</v>
+        <v>0.99929202428944564</v>
       </c>
       <c r="N104">
-        <v>6.3641433898514205E-2</v>
+        <v>1.4159514211089521E-3</v>
       </c>
       <c r="O104">
-        <v>0.99977464788732395</v>
+        <v>1</v>
       </c>
       <c r="P104">
-        <v>4.5070422535209442E-4</v>
+        <v>0</v>
       </c>
       <c r="Q104">
-        <v>0.98182847467571899</v>
+        <v>0.98437728326295537</v>
       </c>
       <c r="R104">
-        <v>3.6343050648562157E-2</v>
+        <v>3.1245433474089219E-2</v>
       </c>
       <c r="S104">
-        <v>0.99165688575899846</v>
+        <v>1</v>
       </c>
       <c r="T104">
-        <v>1.668622848200316E-2</v>
+        <v>0</v>
       </c>
       <c r="U104">
-        <v>0.97291666666666665</v>
+        <v>0.9992819546386299</v>
       </c>
       <c r="V104">
-        <v>5.4166666666666703E-2</v>
+        <v>1.436090722740202E-3</v>
       </c>
       <c r="W104">
-        <v>0.98091697645600995</v>
+        <v>0.98370370370370375</v>
       </c>
       <c r="X104">
-        <v>3.8166047087980187E-2</v>
+        <v>3.2592592592592597E-2</v>
       </c>
       <c r="Y104">
-        <v>0.15795591999999489</v>
+        <v>94.111120780000007</v>
       </c>
       <c r="Z104">
-        <v>5.28228877373111E-3</v>
-      </c>
-    </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.15">
+        <v>10.542140765884829</v>
+      </c>
+    </row>
+    <row r="105" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A105" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B105" t="s">
         <v>52</v>
@@ -8862,75 +8802,75 @@
         <v>29</v>
       </c>
       <c r="E105">
-        <v>1</v>
+        <v>0.9948051948051948</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>1.038961038961039E-2</v>
       </c>
       <c r="G105">
-        <v>1</v>
+        <v>0.97428571428571442</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>5.1428571428571421E-2</v>
       </c>
       <c r="I105">
-        <v>1</v>
+        <v>0.97428571428571442</v>
       </c>
       <c r="J105">
-        <v>0</v>
+        <v>5.1428571428571421E-2</v>
       </c>
       <c r="K105">
-        <v>1</v>
+        <v>0.97428571428571442</v>
       </c>
       <c r="L105">
-        <v>0</v>
+        <v>5.1428571428571421E-2</v>
       </c>
       <c r="M105">
-        <v>1</v>
+        <v>0.96757539795775072</v>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>6.4849204084498402E-2</v>
       </c>
       <c r="O105">
-        <v>1</v>
+        <v>0.99956462585034012</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>8.7074829931972349E-4</v>
       </c>
       <c r="Q105">
-        <v>1</v>
+        <v>0.9695652173913043</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>6.0869565217391307E-2</v>
       </c>
       <c r="S105">
-        <v>1</v>
+        <v>0.99165660630449359</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>1.668678739101272E-2</v>
       </c>
       <c r="U105">
-        <v>1</v>
+        <v>0.97137074829931969</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>5.7258503401360537E-2</v>
       </c>
       <c r="W105">
-        <v>1</v>
+        <v>0.9695652173913043</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>6.0869565217391307E-2</v>
       </c>
       <c r="Y105">
-        <v>29.297437160000051</v>
+        <v>0.13197437999999689</v>
       </c>
       <c r="Z105">
-        <v>0.40394211631131988</v>
-      </c>
-    </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.15">
+        <v>7.7334524710393881E-3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A106" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B106" t="s">
         <v>52</v>
@@ -8942,75 +8882,75 @@
         <v>29</v>
       </c>
       <c r="E106">
-        <v>0.99220779220779209</v>
+        <v>1</v>
       </c>
       <c r="F106">
-        <v>1.038961038961039E-2</v>
+        <v>0</v>
       </c>
       <c r="G106">
-        <v>0.95833333333333326</v>
+        <v>1</v>
       </c>
       <c r="H106">
-        <v>5.2704627669472988E-2</v>
+        <v>0</v>
       </c>
       <c r="I106">
-        <v>0.99787726358148876</v>
+        <v>1</v>
       </c>
       <c r="J106">
-        <v>2.8219988371461992E-3</v>
+        <v>0</v>
       </c>
       <c r="K106">
-        <v>0.9722593353888318</v>
+        <v>1</v>
       </c>
       <c r="L106">
-        <v>3.5742988721422959E-2</v>
+        <v>0</v>
       </c>
       <c r="M106">
-        <v>0.99785827753511858</v>
+        <v>1</v>
       </c>
       <c r="N106">
-        <v>2.8503603222136751E-3</v>
+        <v>0</v>
       </c>
       <c r="O106">
-        <v>0.9999413145539906</v>
+        <v>1</v>
       </c>
       <c r="P106">
-        <v>1.173708920187977E-4</v>
+        <v>0</v>
       </c>
       <c r="Q106">
-        <v>0.95808824908720847</v>
+        <v>1</v>
       </c>
       <c r="R106">
-        <v>5.619041616054446E-2</v>
+        <v>0</v>
       </c>
       <c r="S106">
-        <v>0.99999021909233188</v>
+        <v>1</v>
       </c>
       <c r="T106">
-        <v>1.9561815336466282E-5</v>
+        <v>0</v>
       </c>
       <c r="U106">
-        <v>0.99784083474691199</v>
+        <v>1</v>
       </c>
       <c r="V106">
-        <v>2.8625572850156798E-3</v>
+        <v>0</v>
       </c>
       <c r="W106">
-        <v>0.95536598728906408</v>
+        <v>1</v>
       </c>
       <c r="X106">
-        <v>6.0312233573998522E-2</v>
+        <v>0</v>
       </c>
       <c r="Y106">
-        <v>0.1653757199999745</v>
+        <v>8.6434992800000376</v>
       </c>
       <c r="Z106">
-        <v>5.1548752138072676E-3</v>
-      </c>
-    </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.15">
+        <v>1.2848892600363531</v>
+      </c>
+    </row>
+    <row r="107" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A107" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B107" t="s">
         <v>52</v>
@@ -9022,34 +8962,34 @@
         <v>29</v>
       </c>
       <c r="E107">
-        <v>1</v>
+        <v>0.99220779220779209</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>6.3623110202160492E-3</v>
       </c>
       <c r="G107">
-        <v>1</v>
+        <v>0.98193466353677616</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>3.2671446853855382E-2</v>
       </c>
       <c r="I107">
-        <v>1</v>
+        <v>0.93333333333333324</v>
       </c>
       <c r="J107">
-        <v>0</v>
+        <v>5.6519416526043913E-2</v>
       </c>
       <c r="K107">
-        <v>1</v>
+        <v>0.94596240638793816</v>
       </c>
       <c r="L107">
-        <v>0</v>
+        <v>5.1179673602798889E-2</v>
       </c>
       <c r="M107">
-        <v>1</v>
+        <v>0.9170789668234548</v>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>7.1471653613085939E-2</v>
       </c>
       <c r="O107">
         <v>1</v>
@@ -9058,10 +8998,10 @@
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>1</v>
+        <v>0.95117122923097563</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>4.0215724123578378E-2</v>
       </c>
       <c r="S107">
         <v>1</v>
@@ -9070,27 +9010,27 @@
         <v>0</v>
       </c>
       <c r="U107">
-        <v>1</v>
+        <v>0.92334920634920636</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>6.5655559268328431E-2</v>
       </c>
       <c r="W107">
-        <v>1</v>
+        <v>0.94940328885536585</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>4.179082572384106E-2</v>
       </c>
       <c r="Y107">
-        <v>55.038672440000028</v>
+        <v>0.1161875799999962</v>
       </c>
       <c r="Z107">
-        <v>0.16576245620962801</v>
-      </c>
-    </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.15">
+        <v>1.6395132697283151E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A108" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B108" t="s">
         <v>52</v>
@@ -9102,75 +9042,75 @@
         <v>29</v>
       </c>
       <c r="E108">
-        <v>0.9948051948051948</v>
+        <v>0.9974025974025974</v>
       </c>
       <c r="F108">
-        <v>6.3623110202160492E-3</v>
+        <v>5.1948051948051974E-3</v>
       </c>
       <c r="G108">
-        <v>0.96666666666666656</v>
+        <v>0.99929577464788721</v>
       </c>
       <c r="H108">
-        <v>4.0824829046386318E-2</v>
+        <v>1.40845070422535E-3</v>
       </c>
       <c r="I108">
-        <v>0.99858148893360155</v>
+        <v>0.98333333333333317</v>
       </c>
       <c r="J108">
-        <v>1.7373869734344351E-3</v>
+        <v>3.3333333333333347E-2</v>
       </c>
       <c r="K108">
-        <v>0.97928567784070619</v>
+        <v>0.989645390070922</v>
       </c>
       <c r="L108">
-        <v>2.536976111165044E-2</v>
+        <v>2.070921985815604E-2</v>
       </c>
       <c r="M108">
-        <v>0.99857387984021528</v>
+        <v>0.98072040072196887</v>
       </c>
       <c r="N108">
-        <v>1.7467073519432229E-3</v>
+        <v>3.8559198556062102E-2</v>
       </c>
       <c r="O108">
-        <v>0.99989795918367341</v>
+        <v>1</v>
       </c>
       <c r="P108">
-        <v>2.040816326530415E-4</v>
+        <v>0</v>
       </c>
       <c r="Q108">
-        <v>0.9706496203894277</v>
+        <v>0.98437728326295537</v>
       </c>
       <c r="R108">
-        <v>3.6071390987749828E-2</v>
+        <v>3.1245433474089219E-2</v>
       </c>
       <c r="S108">
-        <v>0.99998993963782701</v>
+        <v>1</v>
       </c>
       <c r="T108">
-        <v>2.0120724346073259E-5</v>
+        <v>0</v>
       </c>
       <c r="U108">
-        <v>0.99854896144135097</v>
+        <v>0.9813492063492063</v>
       </c>
       <c r="V108">
-        <v>1.777309185967704E-3</v>
+        <v>3.7301587301587308E-2</v>
       </c>
       <c r="W108">
-        <v>0.96944444444444444</v>
+        <v>0.98370370370370375</v>
       </c>
       <c r="X108">
-        <v>3.7561107048230277E-2</v>
+        <v>3.2592592592592597E-2</v>
       </c>
       <c r="Y108">
-        <v>3.7486780199999878</v>
+        <v>0.35636941999998728</v>
       </c>
       <c r="Z108">
-        <v>8.4508743030560066E-2</v>
-      </c>
-    </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.15">
+        <v>1.7535286886670109E-2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A109" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B109" t="s">
         <v>52</v>
@@ -9182,78 +9122,78 @@
         <v>29</v>
       </c>
       <c r="E109">
-        <v>0.90146520146520148</v>
+        <v>0.9974025974025974</v>
       </c>
       <c r="F109">
-        <v>3.0477517791271221E-2</v>
+        <v>5.1948051948051974E-3</v>
       </c>
       <c r="G109">
-        <v>0.80876373626373632</v>
+        <v>0.98333333333333317</v>
       </c>
       <c r="H109">
-        <v>1.2835404747118031E-2</v>
+        <v>3.3333333333333347E-2</v>
       </c>
       <c r="I109">
-        <v>0.97303822937625761</v>
+        <v>0.99929577464788721</v>
       </c>
       <c r="J109">
-        <v>8.4291787749379756E-3</v>
+        <v>1.40845070422535E-3</v>
       </c>
       <c r="K109">
-        <v>0.83011105438579269</v>
+        <v>0.989645390070922</v>
       </c>
       <c r="L109">
-        <v>2.1493499488142331E-2</v>
+        <v>2.070921985815604E-2</v>
       </c>
       <c r="M109">
-        <v>0.97174307866051313</v>
+        <v>0.99929202428944564</v>
       </c>
       <c r="N109">
-        <v>9.2036789249722792E-3</v>
+        <v>1.4159514211089521E-3</v>
       </c>
       <c r="O109">
-        <v>0.9998826291079812</v>
+        <v>1</v>
       </c>
       <c r="P109">
-        <v>2.3474178403755101E-4</v>
+        <v>0</v>
       </c>
       <c r="Q109">
-        <v>0.67107713167876715</v>
+        <v>0.98437728326295537</v>
       </c>
       <c r="R109">
-        <v>5.6620680466757237E-2</v>
+        <v>3.1245433474089219E-2</v>
       </c>
       <c r="S109">
-        <v>0.99999021909233166</v>
+        <v>1</v>
       </c>
       <c r="T109">
-        <v>1.9561815336455179E-5</v>
+        <v>0</v>
       </c>
       <c r="U109">
-        <v>0.97383859770700654</v>
+        <v>0.9992819546386299</v>
       </c>
       <c r="V109">
-        <v>7.7809220255613759E-3</v>
+        <v>1.436090722740202E-3</v>
       </c>
       <c r="W109">
-        <v>0.61169921470304744</v>
+        <v>0.98370370370370375</v>
       </c>
       <c r="X109">
-        <v>7.5191042990073315E-2</v>
+        <v>3.2592592592592597E-2</v>
       </c>
       <c r="Y109">
-        <v>9.4122378600000047</v>
+        <v>3.1092247600000058</v>
       </c>
       <c r="Z109">
-        <v>5.5033340681571487E-2</v>
-      </c>
-    </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.15">
+        <v>0.1581237248902693</v>
+      </c>
+    </row>
+    <row r="110" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A110" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B110" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C110" t="s">
         <v>28</v>
@@ -9262,78 +9202,78 @@
         <v>29</v>
       </c>
       <c r="E110">
-        <v>0.89598179814091117</v>
+        <v>0.9974025974025974</v>
       </c>
       <c r="F110">
-        <v>9.0782078003995605E-3</v>
+        <v>5.1948051948051974E-3</v>
       </c>
       <c r="G110">
-        <v>0.77978067461031175</v>
+        <v>0.99929577464788721</v>
       </c>
       <c r="H110">
-        <v>2.5221772544865049E-2</v>
+        <v>1.40845070422535E-3</v>
       </c>
       <c r="I110">
-        <v>0.8133496300211418</v>
+        <v>0.98333333333333317</v>
       </c>
       <c r="J110">
-        <v>1.296844094035046E-2</v>
+        <v>3.3333333333333347E-2</v>
       </c>
       <c r="K110">
-        <v>0.79029471363501169</v>
+        <v>0.989645390070922</v>
       </c>
       <c r="L110">
-        <v>1.9007559265886789E-2</v>
+        <v>2.070921985815604E-2</v>
       </c>
       <c r="M110">
-        <v>0.75000079392933117</v>
+        <v>0.98072040072196887</v>
       </c>
       <c r="N110">
-        <v>2.0630808329808011E-2</v>
+        <v>3.8559198556062102E-2</v>
       </c>
       <c r="O110">
-        <v>0.96787344013407695</v>
+        <v>1</v>
       </c>
       <c r="P110">
-        <v>5.7488527628813896E-3</v>
+        <v>0</v>
       </c>
       <c r="Q110">
-        <v>0.71891816706389589</v>
+        <v>0.98437728326295537</v>
       </c>
       <c r="R110">
-        <v>1.6008364335523401E-2</v>
+        <v>3.1245433474089219E-2</v>
       </c>
       <c r="S110">
-        <v>0.80939267616975319</v>
+        <v>1</v>
       </c>
       <c r="T110">
-        <v>2.1860901215473721E-2</v>
+        <v>0</v>
       </c>
       <c r="U110">
-        <v>0.78014796467199798</v>
+        <v>0.9813492063492063</v>
       </c>
       <c r="V110">
-        <v>1.474596985571131E-2</v>
+        <v>3.7301587301587308E-2</v>
       </c>
       <c r="W110">
-        <v>0.71431830380457118</v>
+        <v>0.98370370370370375</v>
       </c>
       <c r="X110">
-        <v>1.8234330998833929E-2</v>
+        <v>3.2592592592592597E-2</v>
       </c>
       <c r="Y110">
-        <v>202.64031660000001</v>
+        <v>0.1245722999999998</v>
       </c>
       <c r="Z110">
-        <v>12.85769335189897</v>
-      </c>
-    </row>
-    <row r="111" spans="1:26" x14ac:dyDescent="0.15">
+        <v>6.1068052580646589E-3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A111" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B111" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C111" t="s">
         <v>28</v>
@@ -9342,78 +9282,78 @@
         <v>29</v>
       </c>
       <c r="E111">
-        <v>0.87847135034452672</v>
+        <v>1</v>
       </c>
       <c r="F111">
-        <v>1.9398019679380828E-2</v>
+        <v>0</v>
       </c>
       <c r="G111">
-        <v>0.76614904111255444</v>
+        <v>1</v>
       </c>
       <c r="H111">
-        <v>2.221657191815429E-2</v>
+        <v>0</v>
       </c>
       <c r="I111">
-        <v>0.82153643254743502</v>
+        <v>1</v>
       </c>
       <c r="J111">
-        <v>2.3511768242317529E-2</v>
+        <v>0</v>
       </c>
       <c r="K111">
-        <v>0.78288042122838442</v>
+        <v>1</v>
       </c>
       <c r="L111">
-        <v>2.1265246409707179E-2</v>
+        <v>0</v>
       </c>
       <c r="M111">
-        <v>0.7653585462013528</v>
+        <v>1</v>
       </c>
       <c r="N111">
-        <v>5.6067066002792487E-2</v>
+        <v>0</v>
       </c>
       <c r="O111">
-        <v>0.96452804941632164</v>
+        <v>1</v>
       </c>
       <c r="P111">
-        <v>5.0613153825983699E-3</v>
+        <v>0</v>
       </c>
       <c r="Q111">
-        <v>0.69479221571104222</v>
+        <v>1</v>
       </c>
       <c r="R111">
-        <v>3.7719070243627521E-2</v>
+        <v>0</v>
       </c>
       <c r="S111">
-        <v>0.81059118912620109</v>
+        <v>1</v>
       </c>
       <c r="T111">
-        <v>2.3878764886338881E-2</v>
+        <v>0</v>
       </c>
       <c r="U111">
-        <v>0.78618663114996956</v>
+        <v>1</v>
       </c>
       <c r="V111">
-        <v>2.041936707598873E-2</v>
+        <v>0</v>
       </c>
       <c r="W111">
-        <v>0.68390494396307999</v>
+        <v>1</v>
       </c>
       <c r="X111">
-        <v>4.1421017095854197E-2</v>
+        <v>0</v>
       </c>
       <c r="Y111">
-        <v>80.441656480000887</v>
+        <v>25.28726451999999</v>
       </c>
       <c r="Z111">
-        <v>0.78561570650520507</v>
-      </c>
-    </row>
-    <row r="112" spans="1:26" x14ac:dyDescent="0.15">
+        <v>0.32369396922137461</v>
+      </c>
+    </row>
+    <row r="112" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A112" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B112" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C112" t="s">
         <v>28</v>
@@ -9422,78 +9362,78 @@
         <v>29</v>
       </c>
       <c r="E112">
-        <v>0.93683518711723346</v>
+        <v>0.9974025974025974</v>
       </c>
       <c r="F112">
-        <v>3.496152345552549E-3</v>
+        <v>5.1948051948051974E-3</v>
       </c>
       <c r="G112">
-        <v>0.78940874435633523</v>
+        <v>0.98333333333333339</v>
       </c>
       <c r="H112">
-        <v>3.0465809766628351E-2</v>
+        <v>3.3333333333333347E-2</v>
       </c>
       <c r="I112">
-        <v>0.74701166526168361</v>
+        <v>0.99928571428571433</v>
       </c>
       <c r="J112">
-        <v>1.6838788422039098E-2</v>
+        <v>1.428571428571424E-3</v>
       </c>
       <c r="K112">
-        <v>0.76163610649281321</v>
+        <v>0.98964028776978419</v>
       </c>
       <c r="L112">
-        <v>1.701419700296557E-2</v>
+        <v>2.0719424460431669E-2</v>
       </c>
       <c r="M112">
-        <v>0.35447547827274778</v>
+        <v>0.99928185555076965</v>
       </c>
       <c r="N112">
-        <v>1.369628122622878E-2</v>
+        <v>1.436288898460614E-3</v>
       </c>
       <c r="O112">
-        <v>0.94678203397522809</v>
+        <v>0.99994897959183682</v>
       </c>
       <c r="P112">
-        <v>8.3357108605486511E-3</v>
+        <v>1.0204081632654289E-4</v>
       </c>
       <c r="Q112">
-        <v>0.80042899594695138</v>
+        <v>0.98627233712647233</v>
       </c>
       <c r="R112">
-        <v>1.146966545929441E-2</v>
+        <v>2.7455325747055288E-2</v>
       </c>
       <c r="S112">
-        <v>0.7876545939612638</v>
+        <v>0.99998993963782701</v>
       </c>
       <c r="T112">
-        <v>2.6644670480773829E-2</v>
+        <v>2.0120724346073259E-5</v>
       </c>
       <c r="U112">
-        <v>0.72806515964928897</v>
+        <v>0.99926700680272107</v>
       </c>
       <c r="V112">
-        <v>1.417965164823656E-2</v>
+        <v>1.465986394557817E-3</v>
       </c>
       <c r="W112">
-        <v>0.79293202708577015</v>
+        <v>0.98574074074074081</v>
       </c>
       <c r="X112">
-        <v>1.045667312710304E-2</v>
+        <v>2.8518518518518519E-2</v>
       </c>
       <c r="Y112">
-        <v>38.963777519999709</v>
+        <v>9.7567619999995261E-2</v>
       </c>
       <c r="Z112">
-        <v>16.99378154592446</v>
+        <v>7.6744903792753272E-3</v>
       </c>
     </row>
     <row r="113" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A113" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B113" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C113" t="s">
         <v>28</v>
@@ -9502,78 +9442,78 @@
         <v>29</v>
       </c>
       <c r="E113">
-        <v>0.94713208726046694</v>
+        <v>1</v>
       </c>
       <c r="F113">
-        <v>3.52147248958586E-3</v>
+        <v>0</v>
       </c>
       <c r="G113">
-        <v>0.83719203365569328</v>
+        <v>1</v>
       </c>
       <c r="H113">
-        <v>5.1656202684046283E-2</v>
+        <v>0</v>
       </c>
       <c r="I113">
-        <v>0.78071596149900535</v>
+        <v>1</v>
       </c>
       <c r="J113">
-        <v>2.42362275484822E-2</v>
+        <v>0</v>
       </c>
       <c r="K113">
-        <v>0.7925425593777311</v>
+        <v>1</v>
       </c>
       <c r="L113">
-        <v>1.42859996312247E-2</v>
+        <v>0</v>
       </c>
       <c r="M113">
-        <v>0.47076371454256449</v>
+        <v>1</v>
       </c>
       <c r="N113">
-        <v>0.1162788309093979</v>
+        <v>0</v>
       </c>
       <c r="O113">
-        <v>0.96239962060503481</v>
+        <v>1</v>
       </c>
       <c r="P113">
-        <v>4.1574790019552619E-3</v>
+        <v>0</v>
       </c>
       <c r="Q113">
-        <v>0.83477078423920958</v>
+        <v>1</v>
       </c>
       <c r="R113">
-        <v>1.197888409850909E-2</v>
+        <v>0</v>
       </c>
       <c r="S113">
-        <v>0.81928376914291901</v>
+        <v>1</v>
       </c>
       <c r="T113">
-        <v>2.674405482885147E-2</v>
+        <v>0</v>
       </c>
       <c r="U113">
-        <v>0.7643292849710166</v>
+        <v>1</v>
       </c>
       <c r="V113">
-        <v>2.5639057833659828E-2</v>
+        <v>0</v>
       </c>
       <c r="W113">
-        <v>0.82895983959974284</v>
+        <v>1</v>
       </c>
       <c r="X113">
-        <v>1.2903573168848119E-2</v>
+        <v>0</v>
       </c>
       <c r="Y113">
-        <v>14.01754165999955</v>
+        <v>11.01138922</v>
       </c>
       <c r="Z113">
-        <v>0.48726741538301271</v>
+        <v>0.1120388191995029</v>
       </c>
     </row>
     <row r="114" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A114" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B114" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C114" t="s">
         <v>28</v>
@@ -9582,78 +9522,78 @@
         <v>29</v>
       </c>
       <c r="E114">
-        <v>0.92859424825968306</v>
+        <v>0.9974025974025974</v>
       </c>
       <c r="F114">
-        <v>1.1376683800636229E-2</v>
+        <v>5.1948051948051974E-3</v>
       </c>
       <c r="G114">
-        <v>0.7833476338459413</v>
+        <v>0.99930555555555556</v>
       </c>
       <c r="H114">
-        <v>3.7563917448985851E-2</v>
+        <v>1.388888888888884E-3</v>
       </c>
       <c r="I114">
-        <v>0.78270617568085921</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J114">
-        <v>2.3162178571849022E-2</v>
+        <v>0.05</v>
       </c>
       <c r="K114">
-        <v>0.77819326044548309</v>
+        <v>0.98298368298368288</v>
       </c>
       <c r="L114">
-        <v>2.9181831207133899E-2</v>
+        <v>3.4032634032634047E-2</v>
       </c>
       <c r="M114">
-        <v>0.53895894666075084</v>
+        <v>0.96817928305074297</v>
       </c>
       <c r="N114">
-        <v>0.1470484418891633</v>
+        <v>6.3641433898514205E-2</v>
       </c>
       <c r="O114">
-        <v>0.95347104682538253</v>
+        <v>0.99977464788732395</v>
       </c>
       <c r="P114">
-        <v>1.43034829243465E-2</v>
+        <v>4.5070422535209442E-4</v>
       </c>
       <c r="Q114">
-        <v>0.78221419593557251</v>
+        <v>0.98182847467571899</v>
       </c>
       <c r="R114">
-        <v>3.2923157639861957E-2</v>
+        <v>3.6343050648562157E-2</v>
       </c>
       <c r="S114">
-        <v>0.80049395119941646</v>
+        <v>0.99165688575899846</v>
       </c>
       <c r="T114">
-        <v>2.8185446966733051E-2</v>
+        <v>1.668622848200316E-2</v>
       </c>
       <c r="U114">
-        <v>0.76182234810877669</v>
+        <v>0.97291666666666665</v>
       </c>
       <c r="V114">
-        <v>2.191529109191085E-2</v>
+        <v>5.4166666666666703E-2</v>
       </c>
       <c r="W114">
-        <v>0.78119017962930293</v>
+        <v>0.98091697645600995</v>
       </c>
       <c r="X114">
-        <v>3.2582901346557752E-2</v>
+        <v>3.8166047087980187E-2</v>
       </c>
       <c r="Y114">
-        <v>0.33372591999941498</v>
+        <v>0.15795591999999489</v>
       </c>
       <c r="Z114">
-        <v>1.2596184316170621E-2</v>
+        <v>5.28228877373111E-3</v>
       </c>
     </row>
     <row r="115" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A115" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B115" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C115" t="s">
         <v>28</v>
@@ -9662,78 +9602,78 @@
         <v>29</v>
       </c>
       <c r="E115">
-        <v>0.91554820722297858</v>
+        <v>1</v>
       </c>
       <c r="F115">
-        <v>1.1828192349119941E-2</v>
+        <v>0</v>
       </c>
       <c r="G115">
-        <v>0.78786725464329188</v>
+        <v>1</v>
       </c>
       <c r="H115">
-        <v>2.3313625178921611E-2</v>
+        <v>0</v>
       </c>
       <c r="I115">
-        <v>0.8132353998849251</v>
+        <v>1</v>
       </c>
       <c r="J115">
-        <v>2.527830342337917E-2</v>
+        <v>0</v>
       </c>
       <c r="K115">
-        <v>0.79701361730594855</v>
+        <v>1</v>
       </c>
       <c r="L115">
-        <v>2.3916562276652089E-2</v>
+        <v>0</v>
       </c>
       <c r="M115">
-        <v>0.71273139695918153</v>
+        <v>1</v>
       </c>
       <c r="N115">
-        <v>5.7171999788804863E-2</v>
+        <v>0</v>
       </c>
       <c r="O115">
-        <v>0.96350217756820378</v>
+        <v>1</v>
       </c>
       <c r="P115">
-        <v>1.1664639765518981E-2</v>
+        <v>0</v>
       </c>
       <c r="Q115">
-        <v>0.7575197873702969</v>
+        <v>1</v>
       </c>
       <c r="R115">
-        <v>3.1740428538597112E-2</v>
+        <v>0</v>
       </c>
       <c r="S115">
-        <v>0.81236464679256104</v>
+        <v>1</v>
       </c>
       <c r="T115">
-        <v>2.6556611052079609E-2</v>
+        <v>0</v>
       </c>
       <c r="U115">
-        <v>0.7872659276470535</v>
+        <v>1</v>
       </c>
       <c r="V115">
-        <v>2.508659253298769E-2</v>
+        <v>0</v>
       </c>
       <c r="W115">
-        <v>0.75644050872298252</v>
+        <v>1</v>
       </c>
       <c r="X115">
-        <v>3.2053811121322447E-2</v>
+        <v>0</v>
       </c>
       <c r="Y115">
-        <v>1.7863182799992501</v>
+        <v>29.297437160000051</v>
       </c>
       <c r="Z115">
-        <v>2.236748070836906E-2</v>
+        <v>0.40394211631131988</v>
       </c>
     </row>
     <row r="116" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A116" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B116" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C116" t="s">
         <v>28</v>
@@ -9742,78 +9682,78 @@
         <v>29</v>
       </c>
       <c r="E116">
-        <v>0.89564051328299532</v>
+        <v>0.99220779220779209</v>
       </c>
       <c r="F116">
-        <v>9.297193767118234E-3</v>
+        <v>1.038961038961039E-2</v>
       </c>
       <c r="G116">
-        <v>0.75194573859041536</v>
+        <v>0.95833333333333326</v>
       </c>
       <c r="H116">
-        <v>1.9323315971712558E-2</v>
+        <v>5.2704627669472988E-2</v>
       </c>
       <c r="I116">
-        <v>0.83828466628308418</v>
+        <v>0.99787726358148876</v>
       </c>
       <c r="J116">
-        <v>1.1997163527198739E-2</v>
+        <v>2.8219988371461992E-3</v>
       </c>
       <c r="K116">
-        <v>0.78268255283234078</v>
+        <v>0.9722593353888318</v>
       </c>
       <c r="L116">
-        <v>1.6627008204771199E-2</v>
+        <v>3.5742988721422959E-2</v>
       </c>
       <c r="M116">
-        <v>0.74250179181251108</v>
+        <v>0.99785827753511858</v>
       </c>
       <c r="N116">
-        <v>2.1933270705139379E-2</v>
+        <v>2.8503603222136751E-3</v>
       </c>
       <c r="O116">
-        <v>0.9662055765514671</v>
+        <v>0.9999413145539906</v>
       </c>
       <c r="P116">
-        <v>3.8148467586396691E-3</v>
+        <v>1.173708920187977E-4</v>
       </c>
       <c r="Q116">
-        <v>0.72681992938672946</v>
+        <v>0.95808824908720847</v>
       </c>
       <c r="R116">
-        <v>2.0165739271077971E-2</v>
+        <v>5.619041616054446E-2</v>
       </c>
       <c r="S116">
-        <v>0.81552357628399097</v>
+        <v>0.99999021909233188</v>
       </c>
       <c r="T116">
-        <v>2.0903632176373279E-2</v>
+        <v>1.9561815336466282E-5</v>
       </c>
       <c r="U116">
-        <v>0.81739055378592462</v>
+        <v>0.99784083474691199</v>
       </c>
       <c r="V116">
-        <v>1.47381558741435E-2</v>
+        <v>2.8625572850156798E-3</v>
       </c>
       <c r="W116">
-        <v>0.7200956543465914</v>
+        <v>0.95536598728906408</v>
       </c>
       <c r="X116">
-        <v>2.1356603071368239E-2</v>
+        <v>6.0312233573998522E-2</v>
       </c>
       <c r="Y116">
-        <v>115.8209805599989</v>
+        <v>0.1653757199999745</v>
       </c>
       <c r="Z116">
-        <v>0.77423200106814161</v>
+        <v>5.1548752138072676E-3</v>
       </c>
     </row>
     <row r="117" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A117" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B117" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C117" t="s">
         <v>28</v>
@@ -9822,78 +9762,78 @@
         <v>29</v>
       </c>
       <c r="E117">
-        <v>0.94129782556158759</v>
+        <v>1</v>
       </c>
       <c r="F117">
-        <v>4.2547057429440979E-3</v>
+        <v>0</v>
       </c>
       <c r="G117">
-        <v>0.810894245382203</v>
+        <v>1</v>
       </c>
       <c r="H117">
-        <v>3.2226295575826562E-2</v>
+        <v>0</v>
       </c>
       <c r="I117">
-        <v>0.78476393776594322</v>
+        <v>1</v>
       </c>
       <c r="J117">
-        <v>1.8339946782697601E-2</v>
+        <v>0</v>
       </c>
       <c r="K117">
-        <v>0.79132743386367987</v>
+        <v>1</v>
       </c>
       <c r="L117">
-        <v>1.7601484167631579E-2</v>
+        <v>0</v>
       </c>
       <c r="M117">
-        <v>0.4924911068770953</v>
+        <v>1</v>
       </c>
       <c r="N117">
-        <v>0.14391411218968639</v>
+        <v>0</v>
       </c>
       <c r="O117">
-        <v>0.95738006975492529</v>
+        <v>1</v>
       </c>
       <c r="P117">
-        <v>1.098560614041732E-2</v>
+        <v>0</v>
       </c>
       <c r="Q117">
-        <v>0.81652144614617406</v>
+        <v>1</v>
       </c>
       <c r="R117">
-        <v>1.3142503469071171E-2</v>
+        <v>0</v>
       </c>
       <c r="S117">
-        <v>0.81239183435906503</v>
+        <v>1</v>
       </c>
       <c r="T117">
-        <v>2.900271184945051E-2</v>
+        <v>0</v>
       </c>
       <c r="U117">
-        <v>0.765108416791909</v>
+        <v>1</v>
       </c>
       <c r="V117">
-        <v>1.9442479477402661E-2</v>
+        <v>0</v>
       </c>
       <c r="W117">
-        <v>0.81238079485178005</v>
+        <v>1</v>
       </c>
       <c r="X117">
-        <v>1.329029797765786E-2</v>
+        <v>0</v>
       </c>
       <c r="Y117">
-        <v>0.47128675999992992</v>
+        <v>55.038672440000028</v>
       </c>
       <c r="Z117">
-        <v>2.6120755835096141E-2</v>
+        <v>0.16576245620962801</v>
       </c>
     </row>
     <row r="118" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A118" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B118" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C118" t="s">
         <v>28</v>
@@ -9902,78 +9842,78 @@
         <v>29</v>
       </c>
       <c r="E118">
-        <v>0.94301485974312271</v>
+        <v>0.9948051948051948</v>
       </c>
       <c r="F118">
-        <v>6.0782729802797151E-3</v>
+        <v>6.3623110202160492E-3</v>
       </c>
       <c r="G118">
-        <v>0.81696344893964468</v>
+        <v>0.96666666666666656</v>
       </c>
       <c r="H118">
-        <v>4.9516228657727299E-2</v>
+        <v>4.0824829046386318E-2</v>
       </c>
       <c r="I118">
-        <v>0.77867690185636163</v>
+        <v>0.99858148893360155</v>
       </c>
       <c r="J118">
-        <v>2.117551660405697E-2</v>
+        <v>1.7373869734344351E-3</v>
       </c>
       <c r="K118">
-        <v>0.78911830945422989</v>
+        <v>0.97928567784070619</v>
       </c>
       <c r="L118">
-        <v>2.4747639849497211E-2</v>
+        <v>2.536976111165044E-2</v>
       </c>
       <c r="M118">
-        <v>0.48325538781537281</v>
+        <v>0.99857387984021528</v>
       </c>
       <c r="N118">
-        <v>0.14152780948596719</v>
+        <v>1.7467073519432229E-3</v>
       </c>
       <c r="O118">
-        <v>0.95501392229099014</v>
+        <v>0.99989795918367341</v>
       </c>
       <c r="P118">
-        <v>1.474600090859437E-2</v>
+        <v>2.040816326530415E-4</v>
       </c>
       <c r="Q118">
-        <v>0.82149818952699527</v>
+        <v>0.9706496203894277</v>
       </c>
       <c r="R118">
-        <v>1.9515759242075621E-2</v>
+        <v>3.6071390987749828E-2</v>
       </c>
       <c r="S118">
-        <v>0.80918146561184767</v>
+        <v>0.99998993963782701</v>
       </c>
       <c r="T118">
-        <v>2.5351690088622311E-2</v>
+        <v>2.0120724346073259E-5</v>
       </c>
       <c r="U118">
-        <v>0.75923025750829498</v>
+        <v>0.99854896144135097</v>
       </c>
       <c r="V118">
-        <v>1.8347569407563241E-2</v>
+        <v>1.777309185967704E-3</v>
       </c>
       <c r="W118">
-        <v>0.81640886191228146</v>
+        <v>0.96944444444444444</v>
       </c>
       <c r="X118">
-        <v>1.9611130806481029E-2</v>
+        <v>3.7561107048230277E-2</v>
       </c>
       <c r="Y118">
-        <v>434.59879974000069</v>
+        <v>3.7486780199999878</v>
       </c>
       <c r="Z118">
-        <v>1.8893327259682511</v>
+        <v>8.4508743030560066E-2</v>
       </c>
     </row>
     <row r="119" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A119" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B119" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C119" t="s">
         <v>28</v>
@@ -9982,75 +9922,75 @@
         <v>29</v>
       </c>
       <c r="E119">
-        <v>0.92516430596570642</v>
+        <v>0.90146520146520148</v>
       </c>
       <c r="F119">
-        <v>7.8576434322345703E-3</v>
+        <v>3.0477517791271221E-2</v>
       </c>
       <c r="G119">
-        <v>0.74459463929371927</v>
+        <v>0.80876373626373632</v>
       </c>
       <c r="H119">
-        <v>1.9931532983724898E-2</v>
+        <v>1.2835404747118031E-2</v>
       </c>
       <c r="I119">
-        <v>0.76859037553188636</v>
+        <v>0.97303822937625761</v>
       </c>
       <c r="J119">
-        <v>1.1028386586300209E-2</v>
+        <v>8.4291787749379756E-3</v>
       </c>
       <c r="K119">
-        <v>0.74623861861947927</v>
+        <v>0.83011105438579269</v>
       </c>
       <c r="L119">
-        <v>1.621193660051903E-2</v>
+        <v>2.1493499488142331E-2</v>
       </c>
       <c r="M119">
-        <v>0.41174681259738449</v>
+        <v>0.97174307866051313</v>
       </c>
       <c r="N119">
-        <v>9.2728270667718424E-2</v>
+        <v>9.2036789249722792E-3</v>
       </c>
       <c r="O119">
-        <v>0.94978539622362346</v>
+        <v>0.9998826291079812</v>
       </c>
       <c r="P119">
-        <v>9.1771699874373773E-3</v>
+        <v>2.3474178403755101E-4</v>
       </c>
       <c r="Q119">
-        <v>0.77407009844775354</v>
+        <v>0.67107713167876715</v>
       </c>
       <c r="R119">
-        <v>1.9924448581017089E-2</v>
+        <v>5.6620680466757237E-2</v>
       </c>
       <c r="S119">
-        <v>0.79040853878805317</v>
+        <v>0.99999021909233166</v>
       </c>
       <c r="T119">
-        <v>2.5449315603472199E-2</v>
+        <v>1.9561815336455179E-5</v>
       </c>
       <c r="U119">
-        <v>0.75186122296691216</v>
+        <v>0.97383859770700654</v>
       </c>
       <c r="V119">
-        <v>1.2613403037527039E-2</v>
+        <v>7.7809220255613759E-3</v>
       </c>
       <c r="W119">
-        <v>0.77218432520666447</v>
+        <v>0.61169921470304744</v>
       </c>
       <c r="X119">
-        <v>1.9674190238763489E-2</v>
+        <v>7.5191042990073315E-2</v>
       </c>
       <c r="Y119">
-        <v>0.73480614000072819</v>
+        <v>9.4122378600000047</v>
       </c>
       <c r="Z119">
-        <v>1.8716407900314591E-2</v>
+        <v>5.5033340681571487E-2</v>
       </c>
     </row>
     <row r="120" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A120" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B120" t="s">
         <v>51</v>
@@ -10062,75 +10002,75 @@
         <v>29</v>
       </c>
       <c r="E120">
-        <v>0.9193247393208489</v>
+        <v>0.89598179814091117</v>
       </c>
       <c r="F120">
-        <v>1.2003283330670821E-2</v>
+        <v>9.0782078003995605E-3</v>
       </c>
       <c r="G120">
-        <v>0.76747648161969384</v>
+        <v>0.77978067461031175</v>
       </c>
       <c r="H120">
-        <v>2.4913792081338291E-2</v>
+        <v>2.5221772544865049E-2</v>
       </c>
       <c r="I120">
-        <v>0.76274558210899102</v>
+        <v>0.8133496300211418</v>
       </c>
       <c r="J120">
-        <v>1.4040397270906261E-2</v>
+        <v>1.296844094035046E-2</v>
       </c>
       <c r="K120">
-        <v>0.76093841503501514</v>
+        <v>0.79029471363501169</v>
       </c>
       <c r="L120">
-        <v>1.6199420117075019E-2</v>
+        <v>1.9007559265886789E-2</v>
       </c>
       <c r="M120">
-        <v>0.53676722926225695</v>
+        <v>0.75000079392933117</v>
       </c>
       <c r="N120">
-        <v>0.14647624292139419</v>
+        <v>2.0630808329808011E-2</v>
       </c>
       <c r="O120">
-        <v>0.96031445436733553</v>
+        <v>0.96787344013407695</v>
       </c>
       <c r="P120">
-        <v>1.116144325316281E-2</v>
+        <v>5.7488527628813896E-3</v>
       </c>
       <c r="Q120">
-        <v>0.75686600646619795</v>
+        <v>0.71891816706389589</v>
       </c>
       <c r="R120">
-        <v>2.9244568592863531E-2</v>
+        <v>1.6008364335523401E-2</v>
       </c>
       <c r="S120">
-        <v>0.79387136792476087</v>
+        <v>0.80939267616975319</v>
       </c>
       <c r="T120">
-        <v>2.2843150350416608E-2</v>
+        <v>2.1860901215473721E-2</v>
       </c>
       <c r="U120">
-        <v>0.73595649526788343</v>
+        <v>0.78014796467199798</v>
       </c>
       <c r="V120">
-        <v>1.126465774916491E-2</v>
+        <v>1.474596985571131E-2</v>
       </c>
       <c r="W120">
-        <v>0.75547906415331489</v>
+        <v>0.71431830380457118</v>
       </c>
       <c r="X120">
-        <v>2.8698132008138359E-2</v>
+        <v>1.8234330998833929E-2</v>
       </c>
       <c r="Y120">
-        <v>285.40938519999838</v>
+        <v>202.64031660000001</v>
       </c>
       <c r="Z120">
-        <v>30.935293623582151</v>
+        <v>12.85769335189897</v>
       </c>
     </row>
     <row r="121" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A121" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B121" t="s">
         <v>51</v>
@@ -10142,75 +10082,75 @@
         <v>29</v>
       </c>
       <c r="E121">
-        <v>0.92859719545189312</v>
+        <v>0.87847135034452672</v>
       </c>
       <c r="F121">
-        <v>1.145468595570946E-2</v>
+        <v>1.9398019679380828E-2</v>
       </c>
       <c r="G121">
-        <v>0.77581603954202738</v>
+        <v>0.76614904111255444</v>
       </c>
       <c r="H121">
-        <v>3.9145685391452037E-2</v>
+        <v>2.221657191815429E-2</v>
       </c>
       <c r="I121">
-        <v>0.79801041025503783</v>
+        <v>0.82153643254743502</v>
       </c>
       <c r="J121">
-        <v>2.6311892438751289E-2</v>
+        <v>2.3511768242317529E-2</v>
       </c>
       <c r="K121">
-        <v>0.78102720918200852</v>
+        <v>0.78288042122838442</v>
       </c>
       <c r="L121">
-        <v>2.6833234393894241E-2</v>
+        <v>2.1265246409707179E-2</v>
       </c>
       <c r="M121">
-        <v>0.48750161802645697</v>
+        <v>0.7653585462013528</v>
       </c>
       <c r="N121">
-        <v>0.12751618133500381</v>
+        <v>5.6067066002792487E-2</v>
       </c>
       <c r="O121">
-        <v>0.96030553345382652</v>
+        <v>0.96452804941632164</v>
       </c>
       <c r="P121">
-        <v>7.7111516536545561E-3</v>
+        <v>5.0613153825983699E-3</v>
       </c>
       <c r="Q121">
-        <v>0.78568419300640124</v>
+        <v>0.69479221571104222</v>
       </c>
       <c r="R121">
-        <v>3.117751002041861E-2</v>
+        <v>3.7719070243627521E-2</v>
       </c>
       <c r="S121">
-        <v>0.800755741595092</v>
+        <v>0.81059118912620109</v>
       </c>
       <c r="T121">
-        <v>1.9828757054834299E-2</v>
+        <v>2.3878764886338881E-2</v>
       </c>
       <c r="U121">
-        <v>0.78141644205796235</v>
+        <v>0.78618663114996956</v>
       </c>
       <c r="V121">
-        <v>3.019396862970513E-2</v>
+        <v>2.041936707598873E-2</v>
       </c>
       <c r="W121">
-        <v>0.78455774682769241</v>
+        <v>0.68390494396307999</v>
       </c>
       <c r="X121">
-        <v>3.099486909051084E-2</v>
+        <v>4.1421017095854197E-2</v>
       </c>
       <c r="Y121">
-        <v>1.146990179999557</v>
+        <v>80.441656480000887</v>
       </c>
       <c r="Z121">
-        <v>5.0622234385949032E-2</v>
+        <v>0.78561570650520507</v>
       </c>
     </row>
     <row r="122" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A122" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B122" t="s">
         <v>51</v>
@@ -10222,75 +10162,75 @@
         <v>29</v>
       </c>
       <c r="E122">
-        <v>0.94095477238834557</v>
+        <v>0.93683518711723346</v>
       </c>
       <c r="F122">
-        <v>5.3771951469708526E-3</v>
+        <v>3.496152345552549E-3</v>
       </c>
       <c r="G122">
-        <v>0.80246177701274424</v>
+        <v>0.78940874435633523</v>
       </c>
       <c r="H122">
-        <v>3.7065289456192391E-2</v>
+        <v>3.0465809766628351E-2</v>
       </c>
       <c r="I122">
-        <v>0.77716296576301735</v>
+        <v>0.74701166526168361</v>
       </c>
       <c r="J122">
-        <v>2.8047936981579719E-2</v>
+        <v>1.6838788422039098E-2</v>
       </c>
       <c r="K122">
-        <v>0.78094859111491921</v>
+        <v>0.76163610649281321</v>
       </c>
       <c r="L122">
-        <v>2.3955249430916089E-2</v>
+        <v>1.701419700296557E-2</v>
       </c>
       <c r="M122">
-        <v>0.47341212207412858</v>
+        <v>0.35447547827274778</v>
       </c>
       <c r="N122">
-        <v>0.1308214145340007</v>
+        <v>1.369628122622878E-2</v>
       </c>
       <c r="O122">
-        <v>0.95293077251374092</v>
+        <v>0.94678203397522809</v>
       </c>
       <c r="P122">
-        <v>1.2748253053171879E-2</v>
+        <v>8.3357108605486511E-3</v>
       </c>
       <c r="Q122">
-        <v>0.81559117123364988</v>
+        <v>0.80042899594695138</v>
       </c>
       <c r="R122">
-        <v>1.7554907743719431E-2</v>
+        <v>1.146966545929441E-2</v>
       </c>
       <c r="S122">
-        <v>0.80816630647331278</v>
+        <v>0.7876545939612638</v>
       </c>
       <c r="T122">
-        <v>3.4647113161630209E-2</v>
+        <v>2.6644670480773829E-2</v>
       </c>
       <c r="U122">
-        <v>0.75913395292862307</v>
+        <v>0.72806515964928897</v>
       </c>
       <c r="V122">
-        <v>2.7358093481639829E-2</v>
+        <v>1.417965164823656E-2</v>
       </c>
       <c r="W122">
-        <v>0.81078615005244059</v>
+        <v>0.79293202708577015</v>
       </c>
       <c r="X122">
-        <v>1.8414292319386391E-2</v>
+        <v>1.045667312710304E-2</v>
       </c>
       <c r="Y122">
-        <v>890.87346260000049</v>
+        <v>38.963777519999709</v>
       </c>
       <c r="Z122">
-        <v>108.5614029690003</v>
+        <v>16.99378154592446</v>
       </c>
     </row>
     <row r="123" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A123" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B123" t="s">
         <v>51</v>
@@ -10302,75 +10242,75 @@
         <v>29</v>
       </c>
       <c r="E123">
-        <v>0.83625046418277316</v>
+        <v>0.94713208726046694</v>
       </c>
       <c r="F123">
-        <v>1.3758323501100249E-2</v>
+        <v>3.52147248958586E-3</v>
       </c>
       <c r="G123">
-        <v>0.72985656606321436</v>
+        <v>0.83719203365569328</v>
       </c>
       <c r="H123">
-        <v>1.234415990858094E-2</v>
+        <v>5.1656202684046283E-2</v>
       </c>
       <c r="I123">
-        <v>0.82160036763722</v>
+        <v>0.78071596149900535</v>
       </c>
       <c r="J123">
-        <v>2.452761947041172E-2</v>
+        <v>2.42362275484822E-2</v>
       </c>
       <c r="K123">
-        <v>0.75314090283981527</v>
+        <v>0.7925425593777311</v>
       </c>
       <c r="L123">
-        <v>1.331500385734603E-2</v>
+        <v>1.42859996312247E-2</v>
       </c>
       <c r="M123">
-        <v>0.77743556164916616</v>
+        <v>0.47076371454256449</v>
       </c>
       <c r="N123">
-        <v>3.7422959556122549E-2</v>
+        <v>0.1162788309093979</v>
       </c>
       <c r="O123">
-        <v>0.95685771427361654</v>
+        <v>0.96239962060503481</v>
       </c>
       <c r="P123">
-        <v>6.0162349116032136E-3</v>
+        <v>4.1574790019552619E-3</v>
       </c>
       <c r="Q123">
-        <v>0.63674540320507655</v>
+        <v>0.83477078423920958</v>
       </c>
       <c r="R123">
-        <v>2.578834986975876E-2</v>
+        <v>1.197888409850909E-2</v>
       </c>
       <c r="S123">
-        <v>0.78725589790084116</v>
+        <v>0.81928376914291901</v>
       </c>
       <c r="T123">
-        <v>1.8752370225776579E-2</v>
+        <v>2.674405482885147E-2</v>
       </c>
       <c r="U123">
-        <v>0.78392374892697769</v>
+        <v>0.7643292849710166</v>
       </c>
       <c r="V123">
-        <v>2.6791842398645981E-2</v>
+        <v>2.5639057833659828E-2</v>
       </c>
       <c r="W123">
-        <v>0.61190997118550094</v>
+        <v>0.82895983959974284</v>
       </c>
       <c r="X123">
-        <v>2.7096832601776911E-2</v>
+        <v>1.2903573168848119E-2</v>
       </c>
       <c r="Y123">
-        <v>0.35815910000019358</v>
+        <v>14.01754165999955</v>
       </c>
       <c r="Z123">
-        <v>1.230600649970855E-2</v>
+        <v>0.48726741538301271</v>
       </c>
     </row>
     <row r="124" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A124" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B124" t="s">
         <v>51</v>
@@ -10382,75 +10322,75 @@
         <v>29</v>
       </c>
       <c r="E124">
-        <v>0.91623136637725244</v>
+        <v>0.92859424825968306</v>
       </c>
       <c r="F124">
-        <v>1.6430817003286451E-2</v>
+        <v>1.1376683800636229E-2</v>
       </c>
       <c r="G124">
-        <v>0.7825638478855087</v>
+        <v>0.7833476338459413</v>
       </c>
       <c r="H124">
-        <v>3.237287084988745E-2</v>
+        <v>3.7563917448985851E-2</v>
       </c>
       <c r="I124">
-        <v>0.79652611261273309</v>
+        <v>0.78270617568085921</v>
       </c>
       <c r="J124">
-        <v>2.0087611989970212E-2</v>
+        <v>2.3162178571849022E-2</v>
       </c>
       <c r="K124">
-        <v>0.78583820697484197</v>
+        <v>0.77819326044548309</v>
       </c>
       <c r="L124">
-        <v>2.5138615183592509E-2</v>
+        <v>2.9181831207133899E-2</v>
       </c>
       <c r="M124">
-        <v>0.61177049304428555</v>
+        <v>0.53895894666075084</v>
       </c>
       <c r="N124">
-        <v>0.12602934130805921</v>
+        <v>0.1470484418891633</v>
       </c>
       <c r="O124">
-        <v>0.95741949386761505</v>
+        <v>0.95347104682538253</v>
       </c>
       <c r="P124">
-        <v>1.2044248142772329E-2</v>
+        <v>1.43034829243465E-2</v>
       </c>
       <c r="Q124">
-        <v>0.75623782590946342</v>
+        <v>0.78221419593557251</v>
       </c>
       <c r="R124">
-        <v>4.2221716220412812E-2</v>
+        <v>3.2923157639861957E-2</v>
       </c>
       <c r="S124">
-        <v>0.80871152072386698</v>
+        <v>0.80049395119941646</v>
       </c>
       <c r="T124">
-        <v>2.588285496390938E-2</v>
+        <v>2.8185446966733051E-2</v>
       </c>
       <c r="U124">
-        <v>0.77328860623590623</v>
+        <v>0.76182234810877669</v>
       </c>
       <c r="V124">
-        <v>2.0605207199377029E-2</v>
+        <v>2.191529109191085E-2</v>
       </c>
       <c r="W124">
-        <v>0.75521849190509827</v>
+        <v>0.78119017962930293</v>
       </c>
       <c r="X124">
-        <v>4.2546894755269397E-2</v>
+        <v>3.2582901346557752E-2</v>
       </c>
       <c r="Y124">
-        <v>902.19075054000064</v>
+        <v>0.33372591999941498</v>
       </c>
       <c r="Z124">
-        <v>17.592844579411189</v>
+        <v>1.2596184316170621E-2</v>
       </c>
     </row>
     <row r="125" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A125" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B125" t="s">
         <v>51</v>
@@ -10462,75 +10402,75 @@
         <v>29</v>
       </c>
       <c r="E125">
-        <v>0.90147713273564278</v>
+        <v>0.91554820722297858</v>
       </c>
       <c r="F125">
-        <v>9.4960921463556006E-3</v>
+        <v>1.1828192349119941E-2</v>
       </c>
       <c r="G125">
-        <v>0.74439859093222105</v>
+        <v>0.78786725464329188</v>
       </c>
       <c r="H125">
-        <v>2.1829986335930359E-2</v>
+        <v>2.3313625178921611E-2</v>
       </c>
       <c r="I125">
-        <v>0.79222558228740148</v>
+        <v>0.8132353998849251</v>
       </c>
       <c r="J125">
-        <v>2.4838178110160619E-2</v>
+        <v>2.527830342337917E-2</v>
       </c>
       <c r="K125">
-        <v>0.76215642936496475</v>
+        <v>0.79701361730594855</v>
       </c>
       <c r="L125">
-        <v>1.9225332379156579E-2</v>
+        <v>2.3916562276652089E-2</v>
       </c>
       <c r="M125">
-        <v>0.60736414762547408</v>
+        <v>0.71273139695918153</v>
       </c>
       <c r="N125">
-        <v>0.13180774086238911</v>
+        <v>5.7171999788804863E-2</v>
       </c>
       <c r="O125">
-        <v>0.95724643728901226</v>
+        <v>0.96350217756820378</v>
       </c>
       <c r="P125">
-        <v>1.220369882895027E-2</v>
+        <v>1.1664639765518981E-2</v>
       </c>
       <c r="Q125">
-        <v>0.72533523111676712</v>
+        <v>0.7575197873702969</v>
       </c>
       <c r="R125">
-        <v>2.6067704622221591E-2</v>
+        <v>3.1740428538597112E-2</v>
       </c>
       <c r="S125">
-        <v>0.79448308449505034</v>
+        <v>0.81236464679256104</v>
       </c>
       <c r="T125">
-        <v>3.0889776177709181E-2</v>
+        <v>2.6556611052079609E-2</v>
       </c>
       <c r="U125">
-        <v>0.76700062680172787</v>
+        <v>0.7872659276470535</v>
       </c>
       <c r="V125">
-        <v>2.3933525477358521E-2</v>
+        <v>2.508659253298769E-2</v>
       </c>
       <c r="W125">
-        <v>0.72290520159255278</v>
+        <v>0.75644050872298252</v>
       </c>
       <c r="X125">
-        <v>2.6037619479078979E-2</v>
+        <v>3.2053811121322447E-2</v>
       </c>
       <c r="Y125">
-        <v>122.8471560200007</v>
+        <v>1.7863182799992501</v>
       </c>
       <c r="Z125">
-        <v>0.67828257863288821</v>
+        <v>2.236748070836906E-2</v>
       </c>
     </row>
     <row r="126" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A126" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B126" t="s">
         <v>51</v>
@@ -10542,69 +10482,869 @@
         <v>29</v>
       </c>
       <c r="E126">
+        <v>0.89564051328299532</v>
+      </c>
+      <c r="F126">
+        <v>9.297193767118234E-3</v>
+      </c>
+      <c r="G126">
+        <v>0.75194573859041536</v>
+      </c>
+      <c r="H126">
+        <v>1.9323315971712558E-2</v>
+      </c>
+      <c r="I126">
+        <v>0.83828466628308418</v>
+      </c>
+      <c r="J126">
+        <v>1.1997163527198739E-2</v>
+      </c>
+      <c r="K126">
+        <v>0.78268255283234078</v>
+      </c>
+      <c r="L126">
+        <v>1.6627008204771199E-2</v>
+      </c>
+      <c r="M126">
+        <v>0.74250179181251108</v>
+      </c>
+      <c r="N126">
+        <v>2.1933270705139379E-2</v>
+      </c>
+      <c r="O126">
+        <v>0.9662055765514671</v>
+      </c>
+      <c r="P126">
+        <v>3.8148467586396691E-3</v>
+      </c>
+      <c r="Q126">
+        <v>0.72681992938672946</v>
+      </c>
+      <c r="R126">
+        <v>2.0165739271077971E-2</v>
+      </c>
+      <c r="S126">
+        <v>0.81552357628399097</v>
+      </c>
+      <c r="T126">
+        <v>2.0903632176373279E-2</v>
+      </c>
+      <c r="U126">
+        <v>0.81739055378592462</v>
+      </c>
+      <c r="V126">
+        <v>1.47381558741435E-2</v>
+      </c>
+      <c r="W126">
+        <v>0.7200956543465914</v>
+      </c>
+      <c r="X126">
+        <v>2.1356603071368239E-2</v>
+      </c>
+      <c r="Y126">
+        <v>115.8209805599989</v>
+      </c>
+      <c r="Z126">
+        <v>0.77423200106814161</v>
+      </c>
+    </row>
+    <row r="127" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A127" t="s">
+        <v>36</v>
+      </c>
+      <c r="B127" t="s">
+        <v>51</v>
+      </c>
+      <c r="C127" t="s">
+        <v>28</v>
+      </c>
+      <c r="D127" t="s">
+        <v>29</v>
+      </c>
+      <c r="E127">
+        <v>0.94129782556158759</v>
+      </c>
+      <c r="F127">
+        <v>4.2547057429440979E-3</v>
+      </c>
+      <c r="G127">
+        <v>0.810894245382203</v>
+      </c>
+      <c r="H127">
+        <v>3.2226295575826562E-2</v>
+      </c>
+      <c r="I127">
+        <v>0.78476393776594322</v>
+      </c>
+      <c r="J127">
+        <v>1.8339946782697601E-2</v>
+      </c>
+      <c r="K127">
+        <v>0.79132743386367987</v>
+      </c>
+      <c r="L127">
+        <v>1.7601484167631579E-2</v>
+      </c>
+      <c r="M127">
+        <v>0.4924911068770953</v>
+      </c>
+      <c r="N127">
+        <v>0.14391411218968639</v>
+      </c>
+      <c r="O127">
+        <v>0.95738006975492529</v>
+      </c>
+      <c r="P127">
+        <v>1.098560614041732E-2</v>
+      </c>
+      <c r="Q127">
+        <v>0.81652144614617406</v>
+      </c>
+      <c r="R127">
+        <v>1.3142503469071171E-2</v>
+      </c>
+      <c r="S127">
+        <v>0.81239183435906503</v>
+      </c>
+      <c r="T127">
+        <v>2.900271184945051E-2</v>
+      </c>
+      <c r="U127">
+        <v>0.765108416791909</v>
+      </c>
+      <c r="V127">
+        <v>1.9442479477402661E-2</v>
+      </c>
+      <c r="W127">
+        <v>0.81238079485178005</v>
+      </c>
+      <c r="X127">
+        <v>1.329029797765786E-2</v>
+      </c>
+      <c r="Y127">
+        <v>0.47128675999992992</v>
+      </c>
+      <c r="Z127">
+        <v>2.6120755835096141E-2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A128" t="s">
+        <v>37</v>
+      </c>
+      <c r="B128" t="s">
+        <v>51</v>
+      </c>
+      <c r="C128" t="s">
+        <v>28</v>
+      </c>
+      <c r="D128" t="s">
+        <v>29</v>
+      </c>
+      <c r="E128">
+        <v>0.94301485974312271</v>
+      </c>
+      <c r="F128">
+        <v>6.0782729802797151E-3</v>
+      </c>
+      <c r="G128">
+        <v>0.81696344893964468</v>
+      </c>
+      <c r="H128">
+        <v>4.9516228657727299E-2</v>
+      </c>
+      <c r="I128">
+        <v>0.77867690185636163</v>
+      </c>
+      <c r="J128">
+        <v>2.117551660405697E-2</v>
+      </c>
+      <c r="K128">
+        <v>0.78911830945422989</v>
+      </c>
+      <c r="L128">
+        <v>2.4747639849497211E-2</v>
+      </c>
+      <c r="M128">
+        <v>0.48325538781537281</v>
+      </c>
+      <c r="N128">
+        <v>0.14152780948596719</v>
+      </c>
+      <c r="O128">
+        <v>0.95501392229099014</v>
+      </c>
+      <c r="P128">
+        <v>1.474600090859437E-2</v>
+      </c>
+      <c r="Q128">
+        <v>0.82149818952699527</v>
+      </c>
+      <c r="R128">
+        <v>1.9515759242075621E-2</v>
+      </c>
+      <c r="S128">
+        <v>0.80918146561184767</v>
+      </c>
+      <c r="T128">
+        <v>2.5351690088622311E-2</v>
+      </c>
+      <c r="U128">
+        <v>0.75923025750829498</v>
+      </c>
+      <c r="V128">
+        <v>1.8347569407563241E-2</v>
+      </c>
+      <c r="W128">
+        <v>0.81640886191228146</v>
+      </c>
+      <c r="X128">
+        <v>1.9611130806481029E-2</v>
+      </c>
+      <c r="Y128">
+        <v>434.59879974000069</v>
+      </c>
+      <c r="Z128">
+        <v>1.8893327259682511</v>
+      </c>
+    </row>
+    <row r="129" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A129" t="s">
+        <v>38</v>
+      </c>
+      <c r="B129" t="s">
+        <v>51</v>
+      </c>
+      <c r="C129" t="s">
+        <v>28</v>
+      </c>
+      <c r="D129" t="s">
+        <v>29</v>
+      </c>
+      <c r="E129">
+        <v>0.92516430596570642</v>
+      </c>
+      <c r="F129">
+        <v>7.8576434322345703E-3</v>
+      </c>
+      <c r="G129">
+        <v>0.74459463929371927</v>
+      </c>
+      <c r="H129">
+        <v>1.9931532983724898E-2</v>
+      </c>
+      <c r="I129">
+        <v>0.76859037553188636</v>
+      </c>
+      <c r="J129">
+        <v>1.1028386586300209E-2</v>
+      </c>
+      <c r="K129">
+        <v>0.74623861861947927</v>
+      </c>
+      <c r="L129">
+        <v>1.621193660051903E-2</v>
+      </c>
+      <c r="M129">
+        <v>0.41174681259738449</v>
+      </c>
+      <c r="N129">
+        <v>9.2728270667718424E-2</v>
+      </c>
+      <c r="O129">
+        <v>0.94978539622362346</v>
+      </c>
+      <c r="P129">
+        <v>9.1771699874373773E-3</v>
+      </c>
+      <c r="Q129">
+        <v>0.77407009844775354</v>
+      </c>
+      <c r="R129">
+        <v>1.9924448581017089E-2</v>
+      </c>
+      <c r="S129">
+        <v>0.79040853878805317</v>
+      </c>
+      <c r="T129">
+        <v>2.5449315603472199E-2</v>
+      </c>
+      <c r="U129">
+        <v>0.75186122296691216</v>
+      </c>
+      <c r="V129">
+        <v>1.2613403037527039E-2</v>
+      </c>
+      <c r="W129">
+        <v>0.77218432520666447</v>
+      </c>
+      <c r="X129">
+        <v>1.9674190238763489E-2</v>
+      </c>
+      <c r="Y129">
+        <v>0.73480614000072819</v>
+      </c>
+      <c r="Z129">
+        <v>1.8716407900314591E-2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A130" t="s">
+        <v>39</v>
+      </c>
+      <c r="B130" t="s">
+        <v>51</v>
+      </c>
+      <c r="C130" t="s">
+        <v>28</v>
+      </c>
+      <c r="D130" t="s">
+        <v>29</v>
+      </c>
+      <c r="E130">
+        <v>0.9193247393208489</v>
+      </c>
+      <c r="F130">
+        <v>1.2003283330670821E-2</v>
+      </c>
+      <c r="G130">
+        <v>0.76747648161969384</v>
+      </c>
+      <c r="H130">
+        <v>2.4913792081338291E-2</v>
+      </c>
+      <c r="I130">
+        <v>0.76274558210899102</v>
+      </c>
+      <c r="J130">
+        <v>1.4040397270906261E-2</v>
+      </c>
+      <c r="K130">
+        <v>0.76093841503501514</v>
+      </c>
+      <c r="L130">
+        <v>1.6199420117075019E-2</v>
+      </c>
+      <c r="M130">
+        <v>0.53676722926225695</v>
+      </c>
+      <c r="N130">
+        <v>0.14647624292139419</v>
+      </c>
+      <c r="O130">
+        <v>0.96031445436733553</v>
+      </c>
+      <c r="P130">
+        <v>1.116144325316281E-2</v>
+      </c>
+      <c r="Q130">
+        <v>0.75686600646619795</v>
+      </c>
+      <c r="R130">
+        <v>2.9244568592863531E-2</v>
+      </c>
+      <c r="S130">
+        <v>0.79387136792476087</v>
+      </c>
+      <c r="T130">
+        <v>2.2843150350416608E-2</v>
+      </c>
+      <c r="U130">
+        <v>0.73595649526788343</v>
+      </c>
+      <c r="V130">
+        <v>1.126465774916491E-2</v>
+      </c>
+      <c r="W130">
+        <v>0.75547906415331489</v>
+      </c>
+      <c r="X130">
+        <v>2.8698132008138359E-2</v>
+      </c>
+      <c r="Y130">
+        <v>285.40938519999838</v>
+      </c>
+      <c r="Z130">
+        <v>30.935293623582151</v>
+      </c>
+    </row>
+    <row r="131" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A131" t="s">
+        <v>40</v>
+      </c>
+      <c r="B131" t="s">
+        <v>51</v>
+      </c>
+      <c r="C131" t="s">
+        <v>28</v>
+      </c>
+      <c r="D131" t="s">
+        <v>29</v>
+      </c>
+      <c r="E131">
+        <v>0.92859719545189312</v>
+      </c>
+      <c r="F131">
+        <v>1.145468595570946E-2</v>
+      </c>
+      <c r="G131">
+        <v>0.77581603954202738</v>
+      </c>
+      <c r="H131">
+        <v>3.9145685391452037E-2</v>
+      </c>
+      <c r="I131">
+        <v>0.79801041025503783</v>
+      </c>
+      <c r="J131">
+        <v>2.6311892438751289E-2</v>
+      </c>
+      <c r="K131">
+        <v>0.78102720918200852</v>
+      </c>
+      <c r="L131">
+        <v>2.6833234393894241E-2</v>
+      </c>
+      <c r="M131">
+        <v>0.48750161802645697</v>
+      </c>
+      <c r="N131">
+        <v>0.12751618133500381</v>
+      </c>
+      <c r="O131">
+        <v>0.96030553345382652</v>
+      </c>
+      <c r="P131">
+        <v>7.7111516536545561E-3</v>
+      </c>
+      <c r="Q131">
+        <v>0.78568419300640124</v>
+      </c>
+      <c r="R131">
+        <v>3.117751002041861E-2</v>
+      </c>
+      <c r="S131">
+        <v>0.800755741595092</v>
+      </c>
+      <c r="T131">
+        <v>1.9828757054834299E-2</v>
+      </c>
+      <c r="U131">
+        <v>0.78141644205796235</v>
+      </c>
+      <c r="V131">
+        <v>3.019396862970513E-2</v>
+      </c>
+      <c r="W131">
+        <v>0.78455774682769241</v>
+      </c>
+      <c r="X131">
+        <v>3.099486909051084E-2</v>
+      </c>
+      <c r="Y131">
+        <v>1.146990179999557</v>
+      </c>
+      <c r="Z131">
+        <v>5.0622234385949032E-2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A132" t="s">
+        <v>41</v>
+      </c>
+      <c r="B132" t="s">
+        <v>51</v>
+      </c>
+      <c r="C132" t="s">
+        <v>28</v>
+      </c>
+      <c r="D132" t="s">
+        <v>29</v>
+      </c>
+      <c r="E132">
+        <v>0.94095477238834557</v>
+      </c>
+      <c r="F132">
+        <v>5.3771951469708526E-3</v>
+      </c>
+      <c r="G132">
+        <v>0.80246177701274424</v>
+      </c>
+      <c r="H132">
+        <v>3.7065289456192391E-2</v>
+      </c>
+      <c r="I132">
+        <v>0.77716296576301735</v>
+      </c>
+      <c r="J132">
+        <v>2.8047936981579719E-2</v>
+      </c>
+      <c r="K132">
+        <v>0.78094859111491921</v>
+      </c>
+      <c r="L132">
+        <v>2.3955249430916089E-2</v>
+      </c>
+      <c r="M132">
+        <v>0.47341212207412858</v>
+      </c>
+      <c r="N132">
+        <v>0.1308214145340007</v>
+      </c>
+      <c r="O132">
+        <v>0.95293077251374092</v>
+      </c>
+      <c r="P132">
+        <v>1.2748253053171879E-2</v>
+      </c>
+      <c r="Q132">
+        <v>0.81559117123364988</v>
+      </c>
+      <c r="R132">
+        <v>1.7554907743719431E-2</v>
+      </c>
+      <c r="S132">
+        <v>0.80816630647331278</v>
+      </c>
+      <c r="T132">
+        <v>3.4647113161630209E-2</v>
+      </c>
+      <c r="U132">
+        <v>0.75913395292862307</v>
+      </c>
+      <c r="V132">
+        <v>2.7358093481639829E-2</v>
+      </c>
+      <c r="W132">
+        <v>0.81078615005244059</v>
+      </c>
+      <c r="X132">
+        <v>1.8414292319386391E-2</v>
+      </c>
+      <c r="Y132">
+        <v>890.87346260000049</v>
+      </c>
+      <c r="Z132">
+        <v>108.5614029690003</v>
+      </c>
+    </row>
+    <row r="133" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A133" t="s">
+        <v>42</v>
+      </c>
+      <c r="B133" t="s">
+        <v>51</v>
+      </c>
+      <c r="C133" t="s">
+        <v>28</v>
+      </c>
+      <c r="D133" t="s">
+        <v>29</v>
+      </c>
+      <c r="E133">
+        <v>0.83625046418277316</v>
+      </c>
+      <c r="F133">
+        <v>1.3758323501100249E-2</v>
+      </c>
+      <c r="G133">
+        <v>0.72985656606321436</v>
+      </c>
+      <c r="H133">
+        <v>1.234415990858094E-2</v>
+      </c>
+      <c r="I133">
+        <v>0.82160036763722</v>
+      </c>
+      <c r="J133">
+        <v>2.452761947041172E-2</v>
+      </c>
+      <c r="K133">
+        <v>0.75314090283981527</v>
+      </c>
+      <c r="L133">
+        <v>1.331500385734603E-2</v>
+      </c>
+      <c r="M133">
+        <v>0.77743556164916616</v>
+      </c>
+      <c r="N133">
+        <v>3.7422959556122549E-2</v>
+      </c>
+      <c r="O133">
+        <v>0.95685771427361654</v>
+      </c>
+      <c r="P133">
+        <v>6.0162349116032136E-3</v>
+      </c>
+      <c r="Q133">
+        <v>0.63674540320507655</v>
+      </c>
+      <c r="R133">
+        <v>2.578834986975876E-2</v>
+      </c>
+      <c r="S133">
+        <v>0.78725589790084116</v>
+      </c>
+      <c r="T133">
+        <v>1.8752370225776579E-2</v>
+      </c>
+      <c r="U133">
+        <v>0.78392374892697769</v>
+      </c>
+      <c r="V133">
+        <v>2.6791842398645981E-2</v>
+      </c>
+      <c r="W133">
+        <v>0.61190997118550094</v>
+      </c>
+      <c r="X133">
+        <v>2.7096832601776911E-2</v>
+      </c>
+      <c r="Y133">
+        <v>0.35815910000019358</v>
+      </c>
+      <c r="Z133">
+        <v>1.230600649970855E-2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A134" t="s">
+        <v>43</v>
+      </c>
+      <c r="B134" t="s">
+        <v>51</v>
+      </c>
+      <c r="C134" t="s">
+        <v>28</v>
+      </c>
+      <c r="D134" t="s">
+        <v>29</v>
+      </c>
+      <c r="E134">
+        <v>0.91623136637725244</v>
+      </c>
+      <c r="F134">
+        <v>1.6430817003286451E-2</v>
+      </c>
+      <c r="G134">
+        <v>0.7825638478855087</v>
+      </c>
+      <c r="H134">
+        <v>3.237287084988745E-2</v>
+      </c>
+      <c r="I134">
+        <v>0.79652611261273309</v>
+      </c>
+      <c r="J134">
+        <v>2.0087611989970212E-2</v>
+      </c>
+      <c r="K134">
+        <v>0.78583820697484197</v>
+      </c>
+      <c r="L134">
+        <v>2.5138615183592509E-2</v>
+      </c>
+      <c r="M134">
+        <v>0.61177049304428555</v>
+      </c>
+      <c r="N134">
+        <v>0.12602934130805921</v>
+      </c>
+      <c r="O134">
+        <v>0.95741949386761505</v>
+      </c>
+      <c r="P134">
+        <v>1.2044248142772329E-2</v>
+      </c>
+      <c r="Q134">
+        <v>0.75623782590946342</v>
+      </c>
+      <c r="R134">
+        <v>4.2221716220412812E-2</v>
+      </c>
+      <c r="S134">
+        <v>0.80871152072386698</v>
+      </c>
+      <c r="T134">
+        <v>2.588285496390938E-2</v>
+      </c>
+      <c r="U134">
+        <v>0.77328860623590623</v>
+      </c>
+      <c r="V134">
+        <v>2.0605207199377029E-2</v>
+      </c>
+      <c r="W134">
+        <v>0.75521849190509827</v>
+      </c>
+      <c r="X134">
+        <v>4.2546894755269397E-2</v>
+      </c>
+      <c r="Y134">
+        <v>902.19075054000064</v>
+      </c>
+      <c r="Z134">
+        <v>17.592844579411189</v>
+      </c>
+    </row>
+    <row r="135" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A135" t="s">
+        <v>44</v>
+      </c>
+      <c r="B135" t="s">
+        <v>51</v>
+      </c>
+      <c r="C135" t="s">
+        <v>28</v>
+      </c>
+      <c r="D135" t="s">
+        <v>29</v>
+      </c>
+      <c r="E135">
+        <v>0.90147713273564278</v>
+      </c>
+      <c r="F135">
+        <v>9.4960921463556006E-3</v>
+      </c>
+      <c r="G135">
+        <v>0.74439859093222105</v>
+      </c>
+      <c r="H135">
+        <v>2.1829986335930359E-2</v>
+      </c>
+      <c r="I135">
+        <v>0.79222558228740148</v>
+      </c>
+      <c r="J135">
+        <v>2.4838178110160619E-2</v>
+      </c>
+      <c r="K135">
+        <v>0.76215642936496475</v>
+      </c>
+      <c r="L135">
+        <v>1.9225332379156579E-2</v>
+      </c>
+      <c r="M135">
+        <v>0.60736414762547408</v>
+      </c>
+      <c r="N135">
+        <v>0.13180774086238911</v>
+      </c>
+      <c r="O135">
+        <v>0.95724643728901226</v>
+      </c>
+      <c r="P135">
+        <v>1.220369882895027E-2</v>
+      </c>
+      <c r="Q135">
+        <v>0.72533523111676712</v>
+      </c>
+      <c r="R135">
+        <v>2.6067704622221591E-2</v>
+      </c>
+      <c r="S135">
+        <v>0.79448308449505034</v>
+      </c>
+      <c r="T135">
+        <v>3.0889776177709181E-2</v>
+      </c>
+      <c r="U135">
+        <v>0.76700062680172787</v>
+      </c>
+      <c r="V135">
+        <v>2.3933525477358521E-2</v>
+      </c>
+      <c r="W135">
+        <v>0.72290520159255278</v>
+      </c>
+      <c r="X135">
+        <v>2.6037619479078979E-2</v>
+      </c>
+      <c r="Y135">
+        <v>122.8471560200007</v>
+      </c>
+      <c r="Z135">
+        <v>0.67828257863288821</v>
+      </c>
+    </row>
+    <row r="136" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A136" t="s">
+        <v>45</v>
+      </c>
+      <c r="B136" t="s">
+        <v>51</v>
+      </c>
+      <c r="C136" t="s">
+        <v>28</v>
+      </c>
+      <c r="D136" t="s">
+        <v>29</v>
+      </c>
+      <c r="E136">
         <v>0.65189769706400713</v>
       </c>
-      <c r="F126">
+      <c r="F136">
         <v>1.4197355493590341E-2</v>
       </c>
-      <c r="G126">
+      <c r="G136">
         <v>0.70102809514102504</v>
       </c>
-      <c r="H126">
+      <c r="H136">
         <v>1.8366153861705089E-2</v>
       </c>
-      <c r="I126">
+      <c r="I136">
         <v>0.85175472341905945</v>
       </c>
-      <c r="J126">
+      <c r="J136">
         <v>1.5653046292521709E-2</v>
       </c>
-      <c r="K126">
+      <c r="K136">
         <v>0.71550819181907399</v>
       </c>
-      <c r="L126">
+      <c r="L136">
         <v>1.37432683322698E-2</v>
       </c>
-      <c r="M126">
+      <c r="M136">
         <v>0.83565658523993458</v>
       </c>
-      <c r="N126">
+      <c r="N136">
         <v>1.554232795324614E-2</v>
       </c>
-      <c r="O126">
+      <c r="O136">
         <v>0.96096304991653891</v>
       </c>
-      <c r="P126">
+      <c r="P136">
         <v>6.2096076305159682E-3</v>
       </c>
-      <c r="Q126">
+      <c r="Q136">
         <v>0.50869003969313253</v>
       </c>
-      <c r="R126">
+      <c r="R136">
         <v>4.0611910908780122E-3</v>
       </c>
-      <c r="S126">
+      <c r="S136">
         <v>0.79753386467641385</v>
       </c>
-      <c r="T126">
+      <c r="T136">
         <v>2.906154694116839E-2</v>
       </c>
-      <c r="U126">
+      <c r="U136">
         <v>0.81904164150909387</v>
       </c>
-      <c r="V126">
+      <c r="V136">
         <v>2.2984454478096671E-2</v>
       </c>
-      <c r="W126">
+      <c r="W136">
         <v>0.40876775087387929</v>
       </c>
-      <c r="X126">
+      <c r="X136">
         <v>8.5376410821480248E-3</v>
       </c>
-      <c r="Y126">
+      <c r="Y136">
         <v>9.4900220600007739</v>
       </c>
-      <c r="Z126">
+      <c r="Z136">
         <v>5.8479777601923147E-2</v>
       </c>
     </row>

--- a/Result/Bearing_Result_30/Result_Bearing_30.xlsx
+++ b/Result/Bearing_Result_30/Result_Bearing_30.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y136"/>
+  <dimension ref="A1:Y139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.625" customWidth="1" min="1" max="1"/>
@@ -2886,7 +2886,7 @@
         <v>0.97021145049807</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>0.0049023242484884</v>
+        <v>0.0049023242484883</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>104.410063485401</v>
@@ -8293,7 +8293,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>MDO</t>
+          <t>MC-RBO</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -8307,76 +8307,76 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.972422356536419</v>
+        <v>0.978546431</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>0.0010311786577848</v>
+        <v>0.003000596</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.856568471476314</v>
+        <v>0.923819316</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.0069502942664859</v>
+        <v>0.021131675</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>0.811314247909136</v>
+        <v>0.815144028</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.0171778625720391</v>
+        <v>0.023686353</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>0.832179215539703</v>
+        <v>0.855624646</v>
       </c>
       <c r="K95" s="3" t="n">
-        <v>0.0105081619783562</v>
+        <v>0.02353464</v>
       </c>
       <c r="L95" s="3" t="n">
-        <v>0.778099285581985</v>
+        <v>0.776197004</v>
       </c>
       <c r="M95" s="3" t="n">
-        <v>0.0229642762479913</v>
+        <v>0.038152513</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>0.974262036125123</v>
+        <v>0.978749402</v>
       </c>
       <c r="O95" s="3" t="n">
-        <v>0.0026053038886185</v>
+        <v>0.003014257</v>
       </c>
       <c r="P95" s="3" t="n">
-        <v>0.757805085101423</v>
+        <v>0.806138263</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>0.0116385239645512</v>
+        <v>0.028811004</v>
       </c>
       <c r="R95" s="3" t="n">
-        <v>0.85483140452105</v>
+        <v>0.893972911</v>
       </c>
       <c r="S95" s="3" t="n">
-        <v>0.0127163035010635</v>
+        <v>0.019816558</v>
       </c>
       <c r="T95" s="3" t="n">
-        <v>0.802661679455157</v>
+        <v>0.812200604</v>
       </c>
       <c r="U95" s="3" t="n">
-        <v>0.0163457099707232</v>
+        <v>0.018028591</v>
       </c>
       <c r="V95" s="3" t="n">
-        <v>0.756406722063879</v>
+        <v>0.799892988</v>
       </c>
       <c r="W95" s="3" t="n">
-        <v>0.0123626909985807</v>
+        <v>0.030004051</v>
       </c>
       <c r="X95" s="3" t="n">
-        <v>1.99461100000016</v>
+        <v>299.641438</v>
       </c>
       <c r="Y95" s="3" t="n">
-        <v>0.046684247472263</v>
+        <v>2.778509145</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>NROMM</t>
+          <t>MDO</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -8390,76 +8390,76 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.966818754182854</v>
+        <v>0.972422356536419</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>0.0016131244875735</v>
+        <v>0.0010311786577848</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.816488544583084</v>
+        <v>0.856568471476314</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.008804578036125599</v>
+        <v>0.0069502942664859</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.845676548758007</v>
+        <v>0.811314247909136</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.0203011939232722</v>
+        <v>0.0171778625720391</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.829491485777735</v>
+        <v>0.832179215539703</v>
       </c>
       <c r="K96" s="3" t="n">
-        <v>0.0124387797365532</v>
+        <v>0.0105081619783562</v>
       </c>
       <c r="L96" s="3" t="n">
-        <v>0.8240536650977101</v>
+        <v>0.778099285581985</v>
       </c>
       <c r="M96" s="3" t="n">
-        <v>0.0285576923196799</v>
+        <v>0.0229642762479913</v>
       </c>
       <c r="N96" s="3" t="n">
-        <v>0.973433397645575</v>
+        <v>0.974262036125123</v>
       </c>
       <c r="O96" s="3" t="n">
-        <v>0.0036410605667229</v>
+        <v>0.0026053038886185</v>
       </c>
       <c r="P96" s="3" t="n">
-        <v>0.733827228365589</v>
+        <v>0.757805085101423</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>0.0168815891826322</v>
+        <v>0.0116385239645512</v>
       </c>
       <c r="R96" s="3" t="n">
-        <v>0.850483323984645</v>
+        <v>0.85483140452105</v>
       </c>
       <c r="S96" s="3" t="n">
-        <v>0.0171129544180656</v>
+        <v>0.0127163035010635</v>
       </c>
       <c r="T96" s="3" t="n">
-        <v>0.834127805201729</v>
+        <v>0.802661679455157</v>
       </c>
       <c r="U96" s="3" t="n">
-        <v>0.0174576608610014</v>
+        <v>0.0163457099707232</v>
       </c>
       <c r="V96" s="3" t="n">
-        <v>0.732803212023252</v>
+        <v>0.756406722063879</v>
       </c>
       <c r="W96" s="3" t="n">
-        <v>0.0163345501989176</v>
+        <v>0.0123626909985807</v>
       </c>
       <c r="X96" s="3" t="n">
-        <v>1902.94947304</v>
+        <v>1.99461100000016</v>
       </c>
       <c r="Y96" s="3" t="n">
-        <v>64.31548164800169</v>
+        <v>0.046684247472263</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>OREM-M</t>
+          <t>NROMM</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -8473,76 +8473,76 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>0.973263005040814</v>
+        <v>0.966818754182854</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>0.0029144861497725</v>
+        <v>0.0016131244875735</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.847165805235739</v>
+        <v>0.816488544583084</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>0.016791358248593</v>
+        <v>0.008804578036125599</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>0.850859556763449</v>
+        <v>0.845676548758007</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>0.0226459430202022</v>
+        <v>0.0203011939232722</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>0.848371731828005</v>
+        <v>0.829491485777735</v>
       </c>
       <c r="K97" s="3" t="n">
-        <v>0.0183394720606881</v>
+        <v>0.0124387797365532</v>
       </c>
       <c r="L97" s="3" t="n">
-        <v>0.827603580808979</v>
+        <v>0.8240536650977101</v>
       </c>
       <c r="M97" s="3" t="n">
-        <v>0.030848690239032</v>
+        <v>0.0285576923196799</v>
       </c>
       <c r="N97" s="3" t="n">
-        <v>0.979207694558603</v>
+        <v>0.973433397645575</v>
       </c>
       <c r="O97" s="3" t="n">
-        <v>0.0035998318259868</v>
+        <v>0.0036410605667229</v>
       </c>
       <c r="P97" s="3" t="n">
-        <v>0.7752716606272479</v>
+        <v>0.733827228365589</v>
       </c>
       <c r="Q97" s="3" t="n">
-        <v>0.0254931531535887</v>
+        <v>0.0168815891826322</v>
       </c>
       <c r="R97" s="3" t="n">
-        <v>0.876034745060684</v>
+        <v>0.850483323984645</v>
       </c>
       <c r="S97" s="3" t="n">
-        <v>0.021384963695412</v>
+        <v>0.0171129544180656</v>
       </c>
       <c r="T97" s="3" t="n">
-        <v>0.841295813586857</v>
+        <v>0.834127805201729</v>
       </c>
       <c r="U97" s="3" t="n">
-        <v>0.0202945140417531</v>
+        <v>0.0174576608610014</v>
       </c>
       <c r="V97" s="3" t="n">
-        <v>0.7750860428022071</v>
+        <v>0.732803212023252</v>
       </c>
       <c r="W97" s="3" t="n">
-        <v>0.0253535457365744</v>
+        <v>0.0163345501989176</v>
       </c>
       <c r="X97" s="3" t="n">
-        <v>9.93999760000151</v>
+        <v>1902.94947304</v>
       </c>
       <c r="Y97" s="3" t="n">
-        <v>0.674377995074525</v>
+        <v>64.31548164800169</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>QC-SMOTE</t>
+          <t>OREM-M</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -8556,76 +8556,76 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>0.977545694750717</v>
+        <v>0.973263005040814</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>0.0016219826369376</v>
+        <v>0.0029144861497725</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.896005839645877</v>
+        <v>0.847165805235739</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>0.0092500990146153</v>
+        <v>0.016791358248593</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>0.832139306283371</v>
+        <v>0.850859556763449</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>0.0136680895372646</v>
+        <v>0.0226459430202022</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>0.858564958557696</v>
+        <v>0.848371731828005</v>
       </c>
       <c r="K98" s="3" t="n">
-        <v>0.0115933797413573</v>
+        <v>0.0183394720606881</v>
       </c>
       <c r="L98" s="3" t="n">
-        <v>0.802510261488082</v>
+        <v>0.827603580808979</v>
       </c>
       <c r="M98" s="3" t="n">
-        <v>0.0210649830479623</v>
+        <v>0.030848690239032</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>0.979725669251258</v>
+        <v>0.979207694558603</v>
       </c>
       <c r="O98" s="3" t="n">
-        <v>0.0025794085420726</v>
+        <v>0.0035998318259868</v>
       </c>
       <c r="P98" s="3" t="n">
-        <v>0.800853312485784</v>
+        <v>0.7752716606272479</v>
       </c>
       <c r="Q98" s="3" t="n">
-        <v>0.0154206066706353</v>
+        <v>0.0254931531535887</v>
       </c>
       <c r="R98" s="3" t="n">
-        <v>0.885810340897827</v>
+        <v>0.876034745060684</v>
       </c>
       <c r="S98" s="3" t="n">
-        <v>0.021235087889519</v>
+        <v>0.021384963695412</v>
       </c>
       <c r="T98" s="3" t="n">
-        <v>0.825023321177291</v>
+        <v>0.841295813586857</v>
       </c>
       <c r="U98" s="3" t="n">
-        <v>0.0105835677088708</v>
+        <v>0.0202945140417531</v>
       </c>
       <c r="V98" s="3" t="n">
-        <v>0.798350347222396</v>
+        <v>0.7750860428022071</v>
       </c>
       <c r="W98" s="3" t="n">
-        <v>0.0159043061886336</v>
+        <v>0.0253535457365744</v>
       </c>
       <c r="X98" s="3" t="n">
-        <v>346.766774639999</v>
+        <v>9.93999760000151</v>
       </c>
       <c r="Y98" s="3" t="n">
-        <v>22.0890299201468</v>
+        <v>0.674377995074525</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>SHSampler</t>
+          <t>QC-SMOTE</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -8639,76 +8639,76 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.952609596182048</v>
+        <v>0.977545694750717</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>0.0037264355814691</v>
+        <v>0.0016219826369376</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.76029142317951</v>
+        <v>0.896005839645877</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.0118914654889844</v>
+        <v>0.0092500990146153</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>0.868716888079918</v>
+        <v>0.832139306283371</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>0.0152522388366948</v>
+        <v>0.0136680895372646</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>0.800748727637265</v>
+        <v>0.858564958557696</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>0.0119215646497545</v>
+        <v>0.0115933797413573</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>0.856836555244797</v>
+        <v>0.802510261488082</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>0.0196842716388234</v>
+        <v>0.0210649830479623</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>0.972977588455204</v>
+        <v>0.979725669251258</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>0.0025743186849025</v>
+        <v>0.0025794085420726</v>
       </c>
       <c r="P99" s="3" t="n">
-        <v>0.678905426467055</v>
+        <v>0.800853312485784</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>0.0219414290649675</v>
+        <v>0.0154206066706353</v>
       </c>
       <c r="R99" s="3" t="n">
-        <v>0.834248636728146</v>
+        <v>0.885810340897827</v>
       </c>
       <c r="S99" s="3" t="n">
-        <v>0.0226944048715419</v>
+        <v>0.021235087889519</v>
       </c>
       <c r="T99" s="3" t="n">
-        <v>0.852826978140764</v>
+        <v>0.825023321177291</v>
       </c>
       <c r="U99" s="3" t="n">
-        <v>0.0140118583309287</v>
+        <v>0.0105835677088708</v>
       </c>
       <c r="V99" s="3" t="n">
-        <v>0.667228808693771</v>
+        <v>0.798350347222396</v>
       </c>
       <c r="W99" s="3" t="n">
-        <v>0.0225395222966608</v>
+        <v>0.0159043061886336</v>
       </c>
       <c r="X99" s="3" t="n">
-        <v>0.417824260001361</v>
+        <v>346.766774639999</v>
       </c>
       <c r="Y99" s="3" t="n">
-        <v>0.0075382565346401</v>
+        <v>22.0890299201468</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>SMOM</t>
+          <t>SHSampler</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -8722,76 +8722,76 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0.97574462211354</v>
+        <v>0.952609596182048</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0.0021480070431749</v>
+        <v>0.0037264355814691</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.8650657075714751</v>
+        <v>0.76029142317951</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0.0102281920532504</v>
+        <v>0.0118914654889844</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0.862482944124901</v>
+        <v>0.868716888079918</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0.0155134287569977</v>
+        <v>0.0152522388366948</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0.863473535758894</v>
+        <v>0.800748727637265</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0.0127960790974248</v>
+        <v>0.0119215646497545</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0.845111983100036</v>
+        <v>0.856836555244797</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0.0200792494975347</v>
+        <v>0.0196842716388234</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0.982092095564138</v>
+        <v>0.972977588455204</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0.0011542280633612</v>
+        <v>0.0025743186849025</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0.795270400788047</v>
+        <v>0.678905426467055</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0.0188904359711442</v>
+        <v>0.0219414290649675</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0.886730543248014</v>
+        <v>0.834248636728146</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0.0162558756761826</v>
+        <v>0.0226944048715419</v>
       </c>
       <c r="T100" s="3" t="n">
-        <v>0.850656331280555</v>
+        <v>0.852826978140764</v>
       </c>
       <c r="U100" s="3" t="n">
-        <v>0.0144861008205244</v>
+        <v>0.0140118583309287</v>
       </c>
       <c r="V100" s="3" t="n">
-        <v>0.795202811895546</v>
+        <v>0.667228808693771</v>
       </c>
       <c r="W100" s="3" t="n">
-        <v>0.0189276204814506</v>
+        <v>0.0225395222966608</v>
       </c>
       <c r="X100" s="3" t="n">
-        <v>140.237652359998</v>
+        <v>0.417824260001361</v>
       </c>
       <c r="Y100" s="3" t="n">
-        <v>15.2565135025485</v>
+        <v>0.0075382565346401</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>SOUP</t>
+          <t>SMOM</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -8805,76 +8805,76 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.969820651398044</v>
+        <v>0.97574462211354</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0.002379765730336</v>
+        <v>0.0021480070431749</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.826828216641103</v>
+        <v>0.8650657075714751</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.0142713744949819</v>
+        <v>0.0102281920532504</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0.842612620989638</v>
+        <v>0.862482944124901</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0.0168678818481378</v>
+        <v>0.0155134287569977</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0.834379090518373</v>
+        <v>0.863473535758894</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0.0134676764433585</v>
+        <v>0.0127960790974248</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0.819494273429373</v>
+        <v>0.845111983100036</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0.0237527155199231</v>
+        <v>0.0200792494975347</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0.975098245788827</v>
+        <v>0.982092095564138</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0.0016305595224368</v>
+        <v>0.0011542280633612</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0.750481002025727</v>
+        <v>0.795270400788047</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0.0197874501720947</v>
+        <v>0.0188904359711442</v>
       </c>
       <c r="R101" s="3" t="n">
-        <v>0.85439792833854</v>
+        <v>0.886730543248014</v>
       </c>
       <c r="S101" s="3" t="n">
-        <v>0.0127779732091964</v>
+        <v>0.0162558756761826</v>
       </c>
       <c r="T101" s="3" t="n">
-        <v>0.831882693740077</v>
+        <v>0.850656331280555</v>
       </c>
       <c r="U101" s="3" t="n">
-        <v>0.0144512657035226</v>
+        <v>0.0144861008205244</v>
       </c>
       <c r="V101" s="3" t="n">
-        <v>0.750229823043746</v>
+        <v>0.795202811895546</v>
       </c>
       <c r="W101" s="3" t="n">
-        <v>0.0197655427046034</v>
+        <v>0.0189276204814506</v>
       </c>
       <c r="X101" s="3" t="n">
-        <v>2378.0563743</v>
+        <v>140.237652359998</v>
       </c>
       <c r="Y101" s="3" t="n">
-        <v>3.58429767784358</v>
+        <v>15.2565135025485</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>SPE</t>
+          <t>SOUP</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -8888,81 +8888,81 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>0.946965993847709</v>
+        <v>0.969820651398044</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>0.0010316444497425</v>
+        <v>0.002379765730336</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>0.757079237140453</v>
+        <v>0.826828216641103</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.0042900449184031</v>
+        <v>0.0142713744949819</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>0.929504660306873</v>
+        <v>0.842612620989638</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>0.010890248549488</v>
+        <v>0.0168678818481378</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>0.809990579412601</v>
+        <v>0.834379090518373</v>
       </c>
       <c r="K102" s="3" t="n">
-        <v>0.0028864291137325</v>
+        <v>0.0134676764433585</v>
       </c>
       <c r="L102" s="3" t="n">
-        <v>0.928174360114537</v>
+        <v>0.819494273429373</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>0.0118486240325476</v>
+        <v>0.023752715519923</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>0.985925195054399</v>
+        <v>0.975098245788827</v>
       </c>
       <c r="O102" s="3" t="n">
-        <v>0.0018826688308996</v>
+        <v>0.0016305595224368</v>
       </c>
       <c r="P102" s="3" t="n">
-        <v>0.693283744692021</v>
+        <v>0.750481002025727</v>
       </c>
       <c r="Q102" s="3" t="n">
-        <v>0.0052671271330355</v>
+        <v>0.0197874501720947</v>
       </c>
       <c r="R102" s="3" t="n">
-        <v>0.912740561112066</v>
+        <v>0.85439792833854</v>
       </c>
       <c r="S102" s="3" t="n">
-        <v>0.0157205441660873</v>
+        <v>0.0127779732091964</v>
       </c>
       <c r="T102" s="3" t="n">
-        <v>0.9167643766122719</v>
+        <v>0.831882693740077</v>
       </c>
       <c r="U102" s="3" t="n">
-        <v>0.0124023777821758</v>
+        <v>0.0144512657035226</v>
       </c>
       <c r="V102" s="3" t="n">
-        <v>0.665319162848359</v>
+        <v>0.750229823043746</v>
       </c>
       <c r="W102" s="3" t="n">
-        <v>0.0038317390289135</v>
+        <v>0.0197655427046034</v>
       </c>
       <c r="X102" s="3" t="n">
-        <v>9.71486904000048</v>
+        <v>2378.0563743</v>
       </c>
       <c r="Y102" s="3" t="n">
-        <v>0.107250686687698</v>
+        <v>3.58429767784358</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>DBCF</t>
+          <t>SPE</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>IR30_SEU</t>
+          <t>IR30_Ottawa</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -8971,76 +8971,76 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0.992207792207792</v>
+        <v>0.946965993847709</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0.006362311020216</v>
+        <v>0.0010316444497425</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0.9819346635367761</v>
+        <v>0.757079237140453</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.0326714468538553</v>
+        <v>0.0042900449184031</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0.957619047619047</v>
+        <v>0.929504660306873</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0.0521564452832102</v>
+        <v>0.010890248549488</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0.962269360824389</v>
+        <v>0.809990579412601</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0.0331192091206913</v>
+        <v>0.0028864291137325</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0.948181539323481</v>
+        <v>0.928174360114537</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0.06510553484763699</v>
+        <v>0.0118486240325476</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0.999663217399635</v>
+        <v>0.985925195054399</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>0.0004627717006695</v>
+        <v>0.0018826688308996</v>
       </c>
       <c r="P103" s="3" t="n">
-        <v>0.952478095065146</v>
+        <v>0.693283744692021</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>0.0394370415408346</v>
+        <v>0.0052671271330355</v>
       </c>
       <c r="R103" s="3" t="n">
-        <v>0.999970240063227</v>
+        <v>0.912740561112066</v>
       </c>
       <c r="S103" s="3" t="n">
-        <v>3.95065411742166e-05</v>
+        <v>0.0157205441660873</v>
       </c>
       <c r="T103" s="3" t="n">
-        <v>0.953532879818594</v>
+        <v>0.9167643766122719</v>
       </c>
       <c r="U103" s="3" t="n">
-        <v>0.0570113004449794</v>
+        <v>0.0124023777821758</v>
       </c>
       <c r="V103" s="3" t="n">
-        <v>0.9503614209004539</v>
+        <v>0.665319162848359</v>
       </c>
       <c r="W103" s="3" t="n">
-        <v>0.0412468076446869</v>
+        <v>0.0038317390289135</v>
       </c>
       <c r="X103" s="3" t="n">
-        <v>7.25421999999999</v>
+        <v>9.71486904000048</v>
       </c>
       <c r="Y103" s="3" t="n">
-        <v>2.05868613182151</v>
+        <v>0.107250686687698</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>DEAHS</t>
+          <t>DBCF</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -9054,76 +9054,76 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>0.997402597402597</v>
+        <v>0.992207792207792</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>0.0051948051948051</v>
+        <v>0.006362311020216</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>0.9833333333333329</v>
+        <v>0.9819346635367761</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.0333333333333333</v>
+        <v>0.0326714468538553</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>0.999295774647887</v>
+        <v>0.957619047619047</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>0.0014084507042253</v>
+        <v>0.0521564452832102</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>0.989645390070922</v>
+        <v>0.962269360824389</v>
       </c>
       <c r="K104" s="3" t="n">
-        <v>0.020709219858156</v>
+        <v>0.0331192091206913</v>
       </c>
       <c r="L104" s="3" t="n">
-        <v>0.999292024289445</v>
+        <v>0.948181539323481</v>
       </c>
       <c r="M104" s="3" t="n">
-        <v>0.0014159514211089</v>
+        <v>0.06510553484763699</v>
       </c>
       <c r="N104" s="3" t="n">
-        <v>1</v>
+        <v>0.999663217399635</v>
       </c>
       <c r="O104" s="3" t="n">
-        <v>0</v>
+        <v>0.0004627717006695</v>
       </c>
       <c r="P104" s="3" t="n">
-        <v>0.984377283262955</v>
+        <v>0.952478095065146</v>
       </c>
       <c r="Q104" s="3" t="n">
-        <v>0.0312454334740892</v>
+        <v>0.0394370415408346</v>
       </c>
       <c r="R104" s="3" t="n">
-        <v>1</v>
+        <v>0.999970240063227</v>
       </c>
       <c r="S104" s="3" t="n">
-        <v>0</v>
+        <v>3.95065411742166e-05</v>
       </c>
       <c r="T104" s="3" t="n">
-        <v>0.99928195463863</v>
+        <v>0.953532879818594</v>
       </c>
       <c r="U104" s="3" t="n">
-        <v>0.0014360907227402</v>
+        <v>0.0570113004449794</v>
       </c>
       <c r="V104" s="3" t="n">
-        <v>0.983703703703703</v>
+        <v>0.9503614209004539</v>
       </c>
       <c r="W104" s="3" t="n">
-        <v>0.0325925925925926</v>
+        <v>0.0412468076446869</v>
       </c>
       <c r="X104" s="3" t="n">
-        <v>94.11112077999999</v>
+        <v>7.25421999999999</v>
       </c>
       <c r="Y104" s="3" t="n">
-        <v>10.5421407658848</v>
+        <v>2.05868613182151</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>EB-SMOTE</t>
+          <t>DEAHS</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -9137,76 +9137,76 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>0.994805194805194</v>
+        <v>0.997402597402597</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>0.0103896103896103</v>
+        <v>0.0051948051948051</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>0.974285714285714</v>
+        <v>0.9833333333333329</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>0.0514285714285714</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>0.974285714285714</v>
+        <v>0.999295774647887</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>0.0514285714285714</v>
+        <v>0.0014084507042253</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>0.974285714285714</v>
+        <v>0.989645390070922</v>
       </c>
       <c r="K105" s="3" t="n">
-        <v>0.0514285714285714</v>
+        <v>0.020709219858156</v>
       </c>
       <c r="L105" s="3" t="n">
-        <v>0.96757539795775</v>
+        <v>0.999292024289445</v>
       </c>
       <c r="M105" s="3" t="n">
-        <v>0.0648492040844984</v>
+        <v>0.0014159514211089</v>
       </c>
       <c r="N105" s="3" t="n">
-        <v>0.99956462585034</v>
+        <v>1</v>
       </c>
       <c r="O105" s="3" t="n">
-        <v>0.0008707482993197</v>
+        <v>0</v>
       </c>
       <c r="P105" s="3" t="n">
-        <v>0.969565217391304</v>
+        <v>0.984377283262955</v>
       </c>
       <c r="Q105" s="3" t="n">
-        <v>0.0608695652173913</v>
+        <v>0.0312454334740892</v>
       </c>
       <c r="R105" s="3" t="n">
-        <v>0.991656606304493</v>
+        <v>1</v>
       </c>
       <c r="S105" s="3" t="n">
-        <v>0.0166867873910127</v>
+        <v>0</v>
       </c>
       <c r="T105" s="3" t="n">
-        <v>0.971370748299319</v>
+        <v>0.99928195463863</v>
       </c>
       <c r="U105" s="3" t="n">
-        <v>0.0572585034013605</v>
+        <v>0.0014360907227402</v>
       </c>
       <c r="V105" s="3" t="n">
-        <v>0.969565217391304</v>
+        <v>0.983703703703703</v>
       </c>
       <c r="W105" s="3" t="n">
-        <v>0.0608695652173913</v>
+        <v>0.0325925925925926</v>
       </c>
       <c r="X105" s="3" t="n">
-        <v>0.131974379999996</v>
+        <v>94.11112077999999</v>
       </c>
       <c r="Y105" s="3" t="n">
-        <v>0.0077334524710393</v>
+        <v>10.5421407658848</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>FRAME</t>
+          <t>EB-SMOTE</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -9220,76 +9220,76 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>1</v>
+        <v>0.994805194805194</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>0.0103896103896103</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>1</v>
+        <v>0.974285714285714</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>0.0514285714285714</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>1</v>
+        <v>0.974285714285714</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>0.0514285714285714</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>1</v>
+        <v>0.974285714285714</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>0.0514285714285714</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>1</v>
+        <v>0.96757539795775</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>0.0648492040844984</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>1</v>
+        <v>0.99956462585034</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>0.0008707482993197</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>1</v>
+        <v>0.969565217391304</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0</v>
+        <v>0.0608695652173913</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>1</v>
+        <v>0.991656606304493</v>
       </c>
       <c r="S106" s="3" t="n">
-        <v>0</v>
+        <v>0.0166867873910127</v>
       </c>
       <c r="T106" s="3" t="n">
-        <v>1</v>
+        <v>0.971370748299319</v>
       </c>
       <c r="U106" s="3" t="n">
-        <v>0</v>
+        <v>0.0572585034013605</v>
       </c>
       <c r="V106" s="3" t="n">
-        <v>1</v>
+        <v>0.969565217391304</v>
       </c>
       <c r="W106" s="3" t="n">
-        <v>0</v>
+        <v>0.0608695652173913</v>
       </c>
       <c r="X106" s="3" t="n">
-        <v>8.643499280000031</v>
+        <v>0.131974379999996</v>
       </c>
       <c r="Y106" s="3" t="n">
-        <v>1.28488926003635</v>
+        <v>0.0077334524710393</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>GLOS</t>
+          <t>FRAME</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -9303,34 +9303,34 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0.992207792207792</v>
+        <v>1</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0.006362311020216</v>
+        <v>0</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0.9819346635367761</v>
+        <v>1</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.0326714468538553</v>
+        <v>0</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0.933333333333333</v>
+        <v>1</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0.0565194165260439</v>
+        <v>0</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0.945962406387938</v>
+        <v>1</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0.0511796736027988</v>
+        <v>0</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0.917078966823454</v>
+        <v>1</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0.0714716536130859</v>
+        <v>0</v>
       </c>
       <c r="N107" s="3" t="n">
         <v>1</v>
@@ -9339,10 +9339,10 @@
         <v>0</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0.951171229230975</v>
+        <v>1</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0.0402157241235783</v>
+        <v>0</v>
       </c>
       <c r="R107" s="3" t="n">
         <v>1</v>
@@ -9351,28 +9351,28 @@
         <v>0</v>
       </c>
       <c r="T107" s="3" t="n">
-        <v>0.923349206349206</v>
+        <v>1</v>
       </c>
       <c r="U107" s="3" t="n">
-        <v>0.0656555592683284</v>
+        <v>0</v>
       </c>
       <c r="V107" s="3" t="n">
-        <v>0.949403288855365</v>
+        <v>1</v>
       </c>
       <c r="W107" s="3" t="n">
-        <v>0.041790825723841</v>
+        <v>0</v>
       </c>
       <c r="X107" s="3" t="n">
-        <v>0.116187579999996</v>
+        <v>8.643499280000031</v>
       </c>
       <c r="Y107" s="3" t="n">
-        <v>0.0163951326972831</v>
+        <v>1.28488926003635</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>ILMNN</t>
+          <t>GLOS</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -9386,34 +9386,34 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0.997402597402597</v>
+        <v>0.992207792207792</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0.0051948051948051</v>
+        <v>0.006362311020216</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>0.999295774647887</v>
+        <v>0.9819346635367761</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>0.0014084507042253</v>
+        <v>0.0326714468538553</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>0.9833333333333329</v>
+        <v>0.933333333333333</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>0.0333333333333333</v>
+        <v>0.0565194165260439</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>0.989645390070922</v>
+        <v>0.945962406387938</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>0.020709219858156</v>
+        <v>0.0511796736027988</v>
       </c>
       <c r="L108" s="3" t="n">
-        <v>0.980720400721968</v>
+        <v>0.917078966823454</v>
       </c>
       <c r="M108" s="3" t="n">
-        <v>0.0385591985560621</v>
+        <v>0.0714716536130859</v>
       </c>
       <c r="N108" s="3" t="n">
         <v>1</v>
@@ -9422,10 +9422,10 @@
         <v>0</v>
       </c>
       <c r="P108" s="3" t="n">
-        <v>0.984377283262955</v>
+        <v>0.951171229230975</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>0.0312454334740892</v>
+        <v>0.0402157241235783</v>
       </c>
       <c r="R108" s="3" t="n">
         <v>1</v>
@@ -9434,28 +9434,28 @@
         <v>0</v>
       </c>
       <c r="T108" s="3" t="n">
-        <v>0.981349206349206</v>
+        <v>0.923349206349206</v>
       </c>
       <c r="U108" s="3" t="n">
-        <v>0.0373015873015873</v>
+        <v>0.0656555592683284</v>
       </c>
       <c r="V108" s="3" t="n">
-        <v>0.983703703703703</v>
+        <v>0.949403288855365</v>
       </c>
       <c r="W108" s="3" t="n">
-        <v>0.0325925925925926</v>
+        <v>0.041790825723841</v>
       </c>
       <c r="X108" s="3" t="n">
-        <v>0.356369419999987</v>
+        <v>0.116187579999996</v>
       </c>
       <c r="Y108" s="3" t="n">
-        <v>0.0175352868866701</v>
+        <v>0.0163951326972831</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>imDEF</t>
+          <t>ILMNN</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -9475,16 +9475,16 @@
         <v>0.0051948051948051</v>
       </c>
       <c r="F109" s="3" t="n">
+        <v>0.999295774647887</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>0.0014084507042253</v>
+      </c>
+      <c r="H109" s="3" t="n">
         <v>0.9833333333333329</v>
       </c>
-      <c r="G109" s="3" t="n">
+      <c r="I109" s="3" t="n">
         <v>0.0333333333333333</v>
-      </c>
-      <c r="H109" s="3" t="n">
-        <v>0.999295774647887</v>
-      </c>
-      <c r="I109" s="3" t="n">
-        <v>0.0014084507042253</v>
       </c>
       <c r="J109" s="3" t="n">
         <v>0.989645390070922</v>
@@ -9493,10 +9493,10 @@
         <v>0.020709219858156</v>
       </c>
       <c r="L109" s="3" t="n">
-        <v>0.999292024289445</v>
+        <v>0.980720400721968</v>
       </c>
       <c r="M109" s="3" t="n">
-        <v>0.0014159514211089</v>
+        <v>0.0385591985560621</v>
       </c>
       <c r="N109" s="3" t="n">
         <v>1</v>
@@ -9517,10 +9517,10 @@
         <v>0</v>
       </c>
       <c r="T109" s="3" t="n">
-        <v>0.99928195463863</v>
+        <v>0.981349206349206</v>
       </c>
       <c r="U109" s="3" t="n">
-        <v>0.0014360907227402</v>
+        <v>0.0373015873015873</v>
       </c>
       <c r="V109" s="3" t="n">
         <v>0.983703703703703</v>
@@ -9529,16 +9529,16 @@
         <v>0.0325925925925926</v>
       </c>
       <c r="X109" s="3" t="n">
-        <v>3.10922476</v>
+        <v>0.356369419999987</v>
       </c>
       <c r="Y109" s="3" t="n">
-        <v>0.158123724890269</v>
+        <v>0.0175352868866701</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>MC-CCR</t>
+          <t>imDEF</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -9558,16 +9558,16 @@
         <v>0.0051948051948051</v>
       </c>
       <c r="F110" s="3" t="n">
+        <v>0.9833333333333329</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="H110" s="3" t="n">
         <v>0.999295774647887</v>
       </c>
-      <c r="G110" s="3" t="n">
+      <c r="I110" s="3" t="n">
         <v>0.0014084507042253</v>
-      </c>
-      <c r="H110" s="3" t="n">
-        <v>0.9833333333333329</v>
-      </c>
-      <c r="I110" s="3" t="n">
-        <v>0.0333333333333333</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0.989645390070922</v>
@@ -9576,10 +9576,10 @@
         <v>0.020709219858156</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0.980720400721968</v>
+        <v>0.999292024289445</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0.0385591985560621</v>
+        <v>0.0014159514211089</v>
       </c>
       <c r="N110" s="3" t="n">
         <v>1</v>
@@ -9600,10 +9600,10 @@
         <v>0</v>
       </c>
       <c r="T110" s="3" t="n">
-        <v>0.981349206349206</v>
+        <v>0.99928195463863</v>
       </c>
       <c r="U110" s="3" t="n">
-        <v>0.0373015873015873</v>
+        <v>0.0014360907227402</v>
       </c>
       <c r="V110" s="3" t="n">
         <v>0.983703703703703</v>
@@ -9612,16 +9612,16 @@
         <v>0.0325925925925926</v>
       </c>
       <c r="X110" s="3" t="n">
-        <v>0.124572299999999</v>
+        <v>3.10922476</v>
       </c>
       <c r="Y110" s="3" t="n">
-        <v>0.0061068052580646</v>
+        <v>0.158123724890269</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>MC-RBO</t>
+          <t>MC-CCR</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -9635,34 +9635,34 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>1</v>
+        <v>0.997402597402597</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>0.0051948051948051</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>1</v>
+        <v>0.999295774647887</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>0.0014084507042253</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>1</v>
+        <v>0.9833333333333329</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>1</v>
+        <v>0.989645390070922</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>0.020709219858156</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>1</v>
+        <v>0.980720400721968</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>0.0385591985560621</v>
       </c>
       <c r="N111" s="3" t="n">
         <v>1</v>
@@ -9671,10 +9671,10 @@
         <v>0</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>1</v>
+        <v>0.984377283262955</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>0.0312454334740892</v>
       </c>
       <c r="R111" s="3" t="n">
         <v>1</v>
@@ -9683,28 +9683,28 @@
         <v>0</v>
       </c>
       <c r="T111" s="3" t="n">
-        <v>1</v>
+        <v>0.981349206349206</v>
       </c>
       <c r="U111" s="3" t="n">
-        <v>0</v>
+        <v>0.0373015873015873</v>
       </c>
       <c r="V111" s="3" t="n">
-        <v>1</v>
+        <v>0.983703703703703</v>
       </c>
       <c r="W111" s="3" t="n">
-        <v>0</v>
+        <v>0.0325925925925926</v>
       </c>
       <c r="X111" s="3" t="n">
-        <v>25.2872645199999</v>
+        <v>0.124572299999999</v>
       </c>
       <c r="Y111" s="3" t="n">
-        <v>0.323693969221374</v>
+        <v>0.0061068052580646</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>MDO</t>
+          <t>MC-RBO</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -9718,76 +9718,76 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0.997402597402597</v>
+        <v>1</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0.0051948051948051</v>
+        <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0.9833333333333329</v>
+        <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0.0333333333333333</v>
+        <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0.999285714285714</v>
+        <v>1</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0.0014285714285714</v>
+        <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0.989640287769784</v>
+        <v>1</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0.0207194244604316</v>
+        <v>0</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0.999281855550769</v>
+        <v>1</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0.0014362888984606</v>
+        <v>0</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0.999948979591836</v>
+        <v>1</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0.0001020408163265</v>
+        <v>0</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0.986272337126472</v>
+        <v>1</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0.0274553257470552</v>
+        <v>0</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0.999989939637827</v>
+        <v>1</v>
       </c>
       <c r="S112" s="3" t="n">
-        <v>2.01207243460732e-05</v>
+        <v>0</v>
       </c>
       <c r="T112" s="3" t="n">
-        <v>0.999267006802721</v>
+        <v>1</v>
       </c>
       <c r="U112" s="3" t="n">
-        <v>0.0014659863945578</v>
+        <v>0</v>
       </c>
       <c r="V112" s="3" t="n">
-        <v>0.98574074074074</v>
+        <v>1</v>
       </c>
       <c r="W112" s="3" t="n">
-        <v>0.0285185185185185</v>
+        <v>0</v>
       </c>
       <c r="X112" s="3" t="n">
-        <v>0.09756761999999521</v>
+        <v>25.2872645199999</v>
       </c>
       <c r="Y112" s="3" t="n">
-        <v>0.0076744903792753</v>
+        <v>0.323693969221374</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>NROMM</t>
+          <t>MDO</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -9801,76 +9801,76 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>1</v>
+        <v>0.997402597402597</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>0</v>
+        <v>0.0051948051948051</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>1</v>
+        <v>0.9833333333333329</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>1</v>
+        <v>0.999285714285714</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>0</v>
+        <v>0.0014285714285714</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>1</v>
+        <v>0.989640287769784</v>
       </c>
       <c r="K113" s="3" t="n">
-        <v>0</v>
+        <v>0.0207194244604316</v>
       </c>
       <c r="L113" s="3" t="n">
-        <v>1</v>
+        <v>0.999281855550769</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>0</v>
+        <v>0.0014362888984606</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>1</v>
+        <v>0.999948979591836</v>
       </c>
       <c r="O113" s="3" t="n">
-        <v>0</v>
+        <v>0.0001020408163265</v>
       </c>
       <c r="P113" s="3" t="n">
-        <v>1</v>
+        <v>0.986272337126472</v>
       </c>
       <c r="Q113" s="3" t="n">
-        <v>0</v>
+        <v>0.0274553257470552</v>
       </c>
       <c r="R113" s="3" t="n">
-        <v>1</v>
+        <v>0.999989939637827</v>
       </c>
       <c r="S113" s="3" t="n">
-        <v>0</v>
+        <v>2.01207243460732e-05</v>
       </c>
       <c r="T113" s="3" t="n">
-        <v>1</v>
+        <v>0.999267006802721</v>
       </c>
       <c r="U113" s="3" t="n">
-        <v>0</v>
+        <v>0.0014659863945578</v>
       </c>
       <c r="V113" s="3" t="n">
-        <v>1</v>
+        <v>0.98574074074074</v>
       </c>
       <c r="W113" s="3" t="n">
-        <v>0</v>
+        <v>0.0285185185185185</v>
       </c>
       <c r="X113" s="3" t="n">
-        <v>11.01138922</v>
+        <v>0.09756761999999521</v>
       </c>
       <c r="Y113" s="3" t="n">
-        <v>0.112038819199502</v>
+        <v>0.0076744903792753</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>OREM-M</t>
+          <t>NROMM</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -9884,76 +9884,76 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0.997402597402597</v>
+        <v>1</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0.0051948051948051</v>
+        <v>0</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0.999305555555555</v>
+        <v>1</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.0013888888888888</v>
+        <v>0</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0.975</v>
+        <v>1</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0.982983682983682</v>
+        <v>1</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0.034032634032634</v>
+        <v>0</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0.968179283050743</v>
+        <v>1</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>0.0636414338985142</v>
+        <v>0</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>0.999774647887324</v>
+        <v>1</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>0.000450704225352</v>
+        <v>0</v>
       </c>
       <c r="P114" s="3" t="n">
-        <v>0.981828474675719</v>
+        <v>1</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>0.0363430506485621</v>
+        <v>0</v>
       </c>
       <c r="R114" s="3" t="n">
-        <v>0.991656885758998</v>
+        <v>1</v>
       </c>
       <c r="S114" s="3" t="n">
-        <v>0.0166862284820031</v>
+        <v>0</v>
       </c>
       <c r="T114" s="3" t="n">
-        <v>0.972916666666666</v>
+        <v>1</v>
       </c>
       <c r="U114" s="3" t="n">
-        <v>0.0541666666666667</v>
+        <v>0</v>
       </c>
       <c r="V114" s="3" t="n">
-        <v>0.9809169764560099</v>
+        <v>1</v>
       </c>
       <c r="W114" s="3" t="n">
-        <v>0.0381660470879801</v>
+        <v>0</v>
       </c>
       <c r="X114" s="3" t="n">
-        <v>0.157955919999994</v>
+        <v>11.01138922</v>
       </c>
       <c r="Y114" s="3" t="n">
-        <v>0.0052822887737311</v>
+        <v>0.112038819199502</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>QC-SMOTE</t>
+          <t>OREM-M</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -9967,76 +9967,76 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>1</v>
+        <v>0.997402597402597</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.0051948051948051</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>1</v>
+        <v>0.999305555555555</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.0013888888888888</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>1</v>
+        <v>0.975</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>1</v>
+        <v>0.982983682983682</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.034032634032634</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>1</v>
+        <v>0.968179283050743</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.0636414338985142</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>1</v>
+        <v>0.999774647887324</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.000450704225352</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>1</v>
+        <v>0.981828474675719</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.0363430506485621</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>1</v>
+        <v>0.991656885758998</v>
       </c>
       <c r="S115" s="3" t="n">
-        <v>0</v>
+        <v>0.0166862284820031</v>
       </c>
       <c r="T115" s="3" t="n">
-        <v>1</v>
+        <v>0.972916666666666</v>
       </c>
       <c r="U115" s="3" t="n">
-        <v>0</v>
+        <v>0.0541666666666667</v>
       </c>
       <c r="V115" s="3" t="n">
-        <v>1</v>
+        <v>0.9809169764560099</v>
       </c>
       <c r="W115" s="3" t="n">
-        <v>0</v>
+        <v>0.0381660470879801</v>
       </c>
       <c r="X115" s="3" t="n">
-        <v>29.29743716</v>
+        <v>0.157955919999994</v>
       </c>
       <c r="Y115" s="3" t="n">
-        <v>0.403942116311319</v>
+        <v>0.0052822887737311</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>SHSampler</t>
+          <t>QC-SMOTE</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -10050,76 +10050,76 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0.992207792207792</v>
+        <v>1</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0.0103896103896103</v>
+        <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0.958333333333333</v>
+        <v>1</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0.0527046276694729</v>
+        <v>0</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0.997877263581488</v>
+        <v>1</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0.0028219988371461</v>
+        <v>0</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0.972259335388831</v>
+        <v>1</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0.0357429887214229</v>
+        <v>0</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0.997858277535118</v>
+        <v>1</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0.0028503603222136</v>
+        <v>0</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0.99994131455399</v>
+        <v>1</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0.0001173708920187</v>
+        <v>0</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0.958088249087208</v>
+        <v>1</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0.0561904161605444</v>
+        <v>0</v>
       </c>
       <c r="R116" s="3" t="n">
-        <v>0.999990219092332</v>
+        <v>1</v>
       </c>
       <c r="S116" s="3" t="n">
-        <v>1.95618153364662e-05</v>
+        <v>0</v>
       </c>
       <c r="T116" s="3" t="n">
-        <v>0.997840834746912</v>
+        <v>1</v>
       </c>
       <c r="U116" s="3" t="n">
-        <v>0.0028625572850156</v>
+        <v>0</v>
       </c>
       <c r="V116" s="3" t="n">
-        <v>0.955365987289064</v>
+        <v>1</v>
       </c>
       <c r="W116" s="3" t="n">
-        <v>0.0603122335739985</v>
+        <v>0</v>
       </c>
       <c r="X116" s="3" t="n">
-        <v>0.165375719999974</v>
+        <v>29.29743716</v>
       </c>
       <c r="Y116" s="3" t="n">
-        <v>0.0051548752138072</v>
+        <v>0.403942116311319</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>SMOM</t>
+          <t>SHSampler</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -10133,76 +10133,76 @@
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>1</v>
+        <v>0.992207792207792</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>0</v>
+        <v>0.0103896103896103</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>1</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>0</v>
+        <v>0.0527046276694729</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>1</v>
+        <v>0.997877263581488</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>0</v>
+        <v>0.0028219988371461</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>1</v>
+        <v>0.972259335388831</v>
       </c>
       <c r="K117" s="3" t="n">
-        <v>0</v>
+        <v>0.0357429887214229</v>
       </c>
       <c r="L117" s="3" t="n">
-        <v>1</v>
+        <v>0.997858277535118</v>
       </c>
       <c r="M117" s="3" t="n">
-        <v>0</v>
+        <v>0.0028503603222136</v>
       </c>
       <c r="N117" s="3" t="n">
-        <v>1</v>
+        <v>0.99994131455399</v>
       </c>
       <c r="O117" s="3" t="n">
-        <v>0</v>
+        <v>0.0001173708920187</v>
       </c>
       <c r="P117" s="3" t="n">
-        <v>1</v>
+        <v>0.958088249087208</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>0</v>
+        <v>0.0561904161605444</v>
       </c>
       <c r="R117" s="3" t="n">
-        <v>1</v>
+        <v>0.999990219092332</v>
       </c>
       <c r="S117" s="3" t="n">
-        <v>0</v>
+        <v>1.95618153364662e-05</v>
       </c>
       <c r="T117" s="3" t="n">
-        <v>1</v>
+        <v>0.997840834746912</v>
       </c>
       <c r="U117" s="3" t="n">
-        <v>0</v>
+        <v>0.0028625572850156</v>
       </c>
       <c r="V117" s="3" t="n">
-        <v>1</v>
+        <v>0.955365987289064</v>
       </c>
       <c r="W117" s="3" t="n">
-        <v>0</v>
+        <v>0.0603122335739985</v>
       </c>
       <c r="X117" s="3" t="n">
-        <v>55.03867244</v>
+        <v>0.165375719999974</v>
       </c>
       <c r="Y117" s="3" t="n">
-        <v>0.165762456209628</v>
+        <v>0.0051548752138072</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>SOUP</t>
+          <t>SMOM</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -10216,76 +10216,76 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.994805194805194</v>
+        <v>1</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.006362311020216</v>
+        <v>0</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.966666666666666</v>
+        <v>1</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.0408248290463863</v>
+        <v>0</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.998581488933601</v>
+        <v>1</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.0017373869734344</v>
+        <v>0</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.979285677840706</v>
+        <v>1</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.0253697611116504</v>
+        <v>0</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.998573879840215</v>
+        <v>1</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.0017467073519432</v>
+        <v>0</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.999897959183673</v>
+        <v>1</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.000204081632653</v>
+        <v>0</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.970649620389427</v>
+        <v>1</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0.0360713909877498</v>
+        <v>0</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0.999989939637827</v>
+        <v>1</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>2.01207243460732e-05</v>
+        <v>0</v>
       </c>
       <c r="T118" s="3" t="n">
-        <v>0.998548961441351</v>
+        <v>1</v>
       </c>
       <c r="U118" s="3" t="n">
-        <v>0.0017773091859677</v>
+        <v>0</v>
       </c>
       <c r="V118" s="3" t="n">
-        <v>0.969444444444444</v>
+        <v>1</v>
       </c>
       <c r="W118" s="3" t="n">
-        <v>0.0375611070482302</v>
+        <v>0</v>
       </c>
       <c r="X118" s="3" t="n">
-        <v>3.74867801999998</v>
+        <v>55.03867244</v>
       </c>
       <c r="Y118" s="3" t="n">
-        <v>0.08450874303056</v>
+        <v>0.165762456209628</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>SPE</t>
+          <t>SOUP</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -10299,81 +10299,81 @@
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>0.901465201465201</v>
+        <v>0.994805194805194</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>0.0304775177912712</v>
+        <v>0.006362311020216</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>0.808763736263736</v>
+        <v>0.966666666666666</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>0.012835404747118</v>
+        <v>0.0408248290463863</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>0.9730382293762569</v>
+        <v>0.998581488933601</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>0.008429178774937899</v>
+        <v>0.0017373869734344</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>0.830111054385792</v>
+        <v>0.979285677840706</v>
       </c>
       <c r="K119" s="3" t="n">
-        <v>0.0214934994881423</v>
+        <v>0.0253697611116504</v>
       </c>
       <c r="L119" s="3" t="n">
-        <v>0.971743078660513</v>
+        <v>0.998573879840215</v>
       </c>
       <c r="M119" s="3" t="n">
-        <v>0.009203678924972199</v>
+        <v>0.0017467073519432</v>
       </c>
       <c r="N119" s="3" t="n">
-        <v>0.999882629107981</v>
+        <v>0.999897959183673</v>
       </c>
       <c r="O119" s="3" t="n">
-        <v>0.0002347417840375</v>
+        <v>0.000204081632653</v>
       </c>
       <c r="P119" s="3" t="n">
-        <v>0.671077131678767</v>
+        <v>0.970649620389427</v>
       </c>
       <c r="Q119" s="3" t="n">
-        <v>0.0566206804667572</v>
+        <v>0.0360713909877498</v>
       </c>
       <c r="R119" s="3" t="n">
-        <v>0.999990219092331</v>
+        <v>0.999989939637827</v>
       </c>
       <c r="S119" s="3" t="n">
-        <v>1.95618153364551e-05</v>
+        <v>2.01207243460732e-05</v>
       </c>
       <c r="T119" s="3" t="n">
-        <v>0.973838597707006</v>
+        <v>0.998548961441351</v>
       </c>
       <c r="U119" s="3" t="n">
-        <v>0.0077809220255613</v>
+        <v>0.0017773091859677</v>
       </c>
       <c r="V119" s="3" t="n">
-        <v>0.611699214703047</v>
+        <v>0.969444444444444</v>
       </c>
       <c r="W119" s="3" t="n">
-        <v>0.0751910429900733</v>
+        <v>0.0375611070482302</v>
       </c>
       <c r="X119" s="3" t="n">
-        <v>9.412237859999999</v>
+        <v>3.74867801999998</v>
       </c>
       <c r="Y119" s="3" t="n">
-        <v>0.0550333406815714</v>
+        <v>0.08450874303056</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>DBCF</t>
+          <t>SPE</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>IR30_XJTU</t>
+          <t>IR30_SEU</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -10382,76 +10382,76 @@
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0.8959817981409109</v>
+        <v>0.901465201465201</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0.0090782078003995</v>
+        <v>0.0304775177912712</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0.779780674610311</v>
+        <v>0.808763736263736</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0.025221772544865</v>
+        <v>0.012835404747118</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0.813349630021141</v>
+        <v>0.9730382293762569</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>0.0129684409403504</v>
+        <v>0.008429178774937899</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>0.790294713635011</v>
+        <v>0.830111054385792</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>0.0190075592658867</v>
+        <v>0.0214934994881423</v>
       </c>
       <c r="L120" s="3" t="n">
-        <v>0.7500007939293309</v>
+        <v>0.971743078660513</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>0.020630808329808</v>
+        <v>0.009203678924972199</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>0.9678734401340769</v>
+        <v>0.999882629107981</v>
       </c>
       <c r="O120" s="3" t="n">
-        <v>0.0057488527628813</v>
+        <v>0.0002347417840375</v>
       </c>
       <c r="P120" s="3" t="n">
-        <v>0.718918167063895</v>
+        <v>0.671077131678767</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>0.0160083643355234</v>
+        <v>0.0566206804667572</v>
       </c>
       <c r="R120" s="3" t="n">
-        <v>0.809392676169753</v>
+        <v>0.999990219092331</v>
       </c>
       <c r="S120" s="3" t="n">
-        <v>0.0218609012154737</v>
+        <v>1.95618153364551e-05</v>
       </c>
       <c r="T120" s="3" t="n">
-        <v>0.780147964671998</v>
+        <v>0.973838597707006</v>
       </c>
       <c r="U120" s="3" t="n">
-        <v>0.0147459698557113</v>
+        <v>0.0077809220255613</v>
       </c>
       <c r="V120" s="3" t="n">
-        <v>0.714318303804571</v>
+        <v>0.611699214703047</v>
       </c>
       <c r="W120" s="3" t="n">
-        <v>0.0182343309988339</v>
+        <v>0.0751910429900733</v>
       </c>
       <c r="X120" s="3" t="n">
-        <v>202.6403166</v>
+        <v>9.412237859999999</v>
       </c>
       <c r="Y120" s="3" t="n">
-        <v>12.8576933518989</v>
+        <v>0.0550333406815714</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>DEAHS</t>
+          <t>DBCF</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -10465,76 +10465,76 @@
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0.8784713503445259</v>
+        <v>0.8959817981409109</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0.0193980196793808</v>
+        <v>0.0090782078003995</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0.766149041112554</v>
+        <v>0.779780674610311</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0.0222165719181542</v>
+        <v>0.025221772544865</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0.821536432547435</v>
+        <v>0.813349630021141</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0.0235117682423175</v>
+        <v>0.0129684409403504</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0.782880421228384</v>
+        <v>0.790294713635011</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0.0212652464097071</v>
+        <v>0.0190075592658867</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0.765358546201352</v>
+        <v>0.7500007939293309</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0.0560670660027924</v>
+        <v>0.020630808329808</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0.964528049416321</v>
+        <v>0.9678734401340769</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0.0050613153825983</v>
+        <v>0.0057488527628813</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0.694792215711042</v>
+        <v>0.718918167063895</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0.0377190702436275</v>
+        <v>0.0160083643355234</v>
       </c>
       <c r="R121" s="3" t="n">
-        <v>0.810591189126201</v>
+        <v>0.809392676169753</v>
       </c>
       <c r="S121" s="3" t="n">
-        <v>0.0238787648863388</v>
+        <v>0.0218609012154737</v>
       </c>
       <c r="T121" s="3" t="n">
-        <v>0.786186631149969</v>
+        <v>0.780147964671998</v>
       </c>
       <c r="U121" s="3" t="n">
-        <v>0.0204193670759887</v>
+        <v>0.0147459698557113</v>
       </c>
       <c r="V121" s="3" t="n">
-        <v>0.68390494396308</v>
+        <v>0.714318303804571</v>
       </c>
       <c r="W121" s="3" t="n">
-        <v>0.0414210170958542</v>
+        <v>0.0182343309988339</v>
       </c>
       <c r="X121" s="3" t="n">
-        <v>80.4416564800008</v>
+        <v>202.6403166</v>
       </c>
       <c r="Y121" s="3" t="n">
-        <v>0.785615706505205</v>
+        <v>12.8576933518989</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>EB-SMOTE</t>
+          <t>DEAHS</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -10548,76 +10548,76 @@
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>0.936835187117233</v>
+        <v>0.8784713503445259</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>0.0034961523455525</v>
+        <v>0.0193980196793808</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>0.789408744356335</v>
+        <v>0.766149041112554</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>0.0304658097666283</v>
+        <v>0.0222165719181542</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>0.7470116652616829</v>
+        <v>0.821536432547435</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>0.0168387884220391</v>
+        <v>0.0235117682423175</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>0.761636106492813</v>
+        <v>0.782880421228384</v>
       </c>
       <c r="K122" s="3" t="n">
-        <v>0.0170141970029655</v>
+        <v>0.0212652464097071</v>
       </c>
       <c r="L122" s="3" t="n">
-        <v>0.354475478272747</v>
+        <v>0.765358546201352</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>0.0136962812262287</v>
+        <v>0.0560670660027924</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>0.946782033975228</v>
+        <v>0.964528049416321</v>
       </c>
       <c r="O122" s="3" t="n">
-        <v>0.008335710860548601</v>
+        <v>0.0050613153825983</v>
       </c>
       <c r="P122" s="3" t="n">
-        <v>0.800428995946951</v>
+        <v>0.694792215711042</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>0.0114696654592944</v>
+        <v>0.0377190702436275</v>
       </c>
       <c r="R122" s="3" t="n">
-        <v>0.787654593961263</v>
+        <v>0.810591189126201</v>
       </c>
       <c r="S122" s="3" t="n">
-        <v>0.0266446704807738</v>
+        <v>0.0238787648863388</v>
       </c>
       <c r="T122" s="3" t="n">
-        <v>0.728065159649289</v>
+        <v>0.786186631149969</v>
       </c>
       <c r="U122" s="3" t="n">
-        <v>0.0141796516482365</v>
+        <v>0.0204193670759887</v>
       </c>
       <c r="V122" s="3" t="n">
-        <v>0.79293202708577</v>
+        <v>0.68390494396308</v>
       </c>
       <c r="W122" s="3" t="n">
-        <v>0.010456673127103</v>
+        <v>0.0414210170958542</v>
       </c>
       <c r="X122" s="3" t="n">
-        <v>38.9637775199997</v>
+        <v>80.4416564800008</v>
       </c>
       <c r="Y122" s="3" t="n">
-        <v>16.9937815459244</v>
+        <v>0.785615706505205</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>FRAME</t>
+          <t>EB-SMOTE</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -10631,76 +10631,76 @@
         </is>
       </c>
       <c r="D123" s="3" t="n">
-        <v>0.947132087260466</v>
+        <v>0.936835187117233</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>0.0035214724895858</v>
+        <v>0.0034961523455525</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>0.8371920336556929</v>
+        <v>0.789408744356335</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>0.0516562026840462</v>
+        <v>0.0304658097666283</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>0.780715961499005</v>
+        <v>0.7470116652616829</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>0.0242362275484822</v>
+        <v>0.0168387884220391</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>0.792542559377731</v>
+        <v>0.761636106492813</v>
       </c>
       <c r="K123" s="3" t="n">
-        <v>0.0142859996312247</v>
+        <v>0.0170141970029655</v>
       </c>
       <c r="L123" s="3" t="n">
-        <v>0.470763714542564</v>
+        <v>0.354475478272747</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>0.116278830909397</v>
+        <v>0.0136962812262287</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>0.962399620605034</v>
+        <v>0.946782033975228</v>
       </c>
       <c r="O123" s="3" t="n">
-        <v>0.0041574790019552</v>
+        <v>0.008335710860548601</v>
       </c>
       <c r="P123" s="3" t="n">
-        <v>0.834770784239209</v>
+        <v>0.800428995946951</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>0.011978884098509</v>
+        <v>0.0114696654592944</v>
       </c>
       <c r="R123" s="3" t="n">
-        <v>0.819283769142919</v>
+        <v>0.787654593961263</v>
       </c>
       <c r="S123" s="3" t="n">
-        <v>0.0267440548288514</v>
+        <v>0.0266446704807738</v>
       </c>
       <c r="T123" s="3" t="n">
-        <v>0.764329284971016</v>
+        <v>0.728065159649289</v>
       </c>
       <c r="U123" s="3" t="n">
-        <v>0.0256390578336598</v>
+        <v>0.0141796516482365</v>
       </c>
       <c r="V123" s="3" t="n">
-        <v>0.828959839599742</v>
+        <v>0.79293202708577</v>
       </c>
       <c r="W123" s="3" t="n">
-        <v>0.0129035731688481</v>
+        <v>0.010456673127103</v>
       </c>
       <c r="X123" s="3" t="n">
-        <v>14.0175416599995</v>
+        <v>38.9637775199997</v>
       </c>
       <c r="Y123" s="3" t="n">
-        <v>0.487267415383012</v>
+        <v>16.9937815459244</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>GLOS</t>
+          <t>FRAME</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -10714,76 +10714,76 @@
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0.928594248259683</v>
+        <v>0.947132087260466</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0.0113766838006362</v>
+        <v>0.0035214724895858</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0.783347633845941</v>
+        <v>0.8371920336556929</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0.0375639174489858</v>
+        <v>0.0516562026840462</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0.782706175680859</v>
+        <v>0.780715961499005</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0.023162178571849</v>
+        <v>0.0242362275484822</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0.778193260445483</v>
+        <v>0.792542559377731</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0.0291818312071339</v>
+        <v>0.0142859996312247</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0.5389589466607499</v>
+        <v>0.470763714542564</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0.147048441889163</v>
+        <v>0.116278830909397</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0.953471046825382</v>
+        <v>0.962399620605034</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0.0143034829243465</v>
+        <v>0.0041574790019552</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0.782214195935572</v>
+        <v>0.834770784239209</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0.0329231576398619</v>
+        <v>0.011978884098509</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0.800493951199416</v>
+        <v>0.819283769142919</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0.028185446966733</v>
+        <v>0.0267440548288514</v>
       </c>
       <c r="T124" s="3" t="n">
-        <v>0.761822348108776</v>
+        <v>0.764329284971016</v>
       </c>
       <c r="U124" s="3" t="n">
-        <v>0.0219152910919108</v>
+        <v>0.0256390578336598</v>
       </c>
       <c r="V124" s="3" t="n">
-        <v>0.781190179629302</v>
+        <v>0.828959839599742</v>
       </c>
       <c r="W124" s="3" t="n">
-        <v>0.0325829013465577</v>
+        <v>0.0129035731688481</v>
       </c>
       <c r="X124" s="3" t="n">
-        <v>0.333725919999415</v>
+        <v>14.0175416599995</v>
       </c>
       <c r="Y124" s="3" t="n">
-        <v>0.0125961843161706</v>
+        <v>0.487267415383012</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>ILMNN</t>
+          <t>GLOS</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -10797,76 +10797,76 @@
         </is>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0.915548207222978</v>
+        <v>0.928594248259683</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0.0118281923491199</v>
+        <v>0.0113766838006362</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0.787867254643291</v>
+        <v>0.783347633845941</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0.0233136251789216</v>
+        <v>0.0375639174489858</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0.813235399884925</v>
+        <v>0.782706175680859</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0.0252783034233791</v>
+        <v>0.023162178571849</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0.797013617305948</v>
+        <v>0.778193260445483</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0.023916562276652</v>
+        <v>0.0291818312071339</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0.712731396959181</v>
+        <v>0.5389589466607499</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0.0571719997888048</v>
+        <v>0.147048441889163</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0.963502177568203</v>
+        <v>0.953471046825382</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0.0116646397655189</v>
+        <v>0.0143034829243465</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0.757519787370296</v>
+        <v>0.782214195935572</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0.0317404285385971</v>
+        <v>0.0329231576398619</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0.812364646792561</v>
+        <v>0.800493951199416</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0.0265566110520796</v>
+        <v>0.028185446966733</v>
       </c>
       <c r="T125" s="3" t="n">
-        <v>0.7872659276470531</v>
+        <v>0.761822348108776</v>
       </c>
       <c r="U125" s="3" t="n">
-        <v>0.0250865925329876</v>
+        <v>0.0219152910919108</v>
       </c>
       <c r="V125" s="3" t="n">
-        <v>0.756440508722982</v>
+        <v>0.781190179629302</v>
       </c>
       <c r="W125" s="3" t="n">
-        <v>0.0320538111213224</v>
+        <v>0.0325829013465577</v>
       </c>
       <c r="X125" s="3" t="n">
-        <v>1.78631827999925</v>
+        <v>0.333725919999415</v>
       </c>
       <c r="Y125" s="3" t="n">
-        <v>0.022367480708369</v>
+        <v>0.0125961843161706</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>imDEF</t>
+          <t>ILMNN</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -10880,76 +10880,76 @@
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0.895640513282995</v>
+        <v>0.915548207222978</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0.009297193767118199</v>
+        <v>0.0118281923491199</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>0.751945738590415</v>
+        <v>0.787867254643291</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>0.0193233159717125</v>
+        <v>0.0233136251789216</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>0.838284666283084</v>
+        <v>0.813235399884925</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0.0119971635271987</v>
+        <v>0.0252783034233791</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>0.78268255283234</v>
+        <v>0.797013617305948</v>
       </c>
       <c r="K126" s="3" t="n">
-        <v>0.0166270082047712</v>
+        <v>0.023916562276652</v>
       </c>
       <c r="L126" s="3" t="n">
-        <v>0.742501791812511</v>
+        <v>0.712731396959181</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>0.0219332707051393</v>
+        <v>0.0571719997888048</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>0.966205576551467</v>
+        <v>0.963502177568203</v>
       </c>
       <c r="O126" s="3" t="n">
-        <v>0.0038148467586396</v>
+        <v>0.0116646397655189</v>
       </c>
       <c r="P126" s="3" t="n">
-        <v>0.726819929386729</v>
+        <v>0.757519787370296</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>0.0201657392710779</v>
+        <v>0.0317404285385971</v>
       </c>
       <c r="R126" s="3" t="n">
-        <v>0.815523576283991</v>
+        <v>0.812364646792561</v>
       </c>
       <c r="S126" s="3" t="n">
-        <v>0.0209036321763732</v>
+        <v>0.0265566110520796</v>
       </c>
       <c r="T126" s="3" t="n">
-        <v>0.817390553785924</v>
+        <v>0.7872659276470531</v>
       </c>
       <c r="U126" s="3" t="n">
-        <v>0.0147381558741435</v>
+        <v>0.0250865925329876</v>
       </c>
       <c r="V126" s="3" t="n">
-        <v>0.720095654346591</v>
+        <v>0.756440508722982</v>
       </c>
       <c r="W126" s="3" t="n">
-        <v>0.0213566030713682</v>
+        <v>0.0320538111213224</v>
       </c>
       <c r="X126" s="3" t="n">
-        <v>115.820980559998</v>
+        <v>1.78631827999925</v>
       </c>
       <c r="Y126" s="3" t="n">
-        <v>0.7742320010681411</v>
+        <v>0.022367480708369</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>MC-CCR</t>
+          <t>imDEF</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -10963,76 +10963,76 @@
         </is>
       </c>
       <c r="D127" s="3" t="n">
-        <v>0.941297825561587</v>
+        <v>0.895640513282995</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>0.004254705742944</v>
+        <v>0.009297193767118199</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>0.810894245382203</v>
+        <v>0.751945738590415</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>0.0322262955758265</v>
+        <v>0.0193233159717125</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>0.784763937765943</v>
+        <v>0.838284666283084</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>0.0183399467826976</v>
+        <v>0.0119971635271987</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>0.791327433863679</v>
+        <v>0.78268255283234</v>
       </c>
       <c r="K127" s="3" t="n">
-        <v>0.0176014841676315</v>
+        <v>0.0166270082047712</v>
       </c>
       <c r="L127" s="3" t="n">
-        <v>0.492491106877095</v>
+        <v>0.742501791812511</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>0.143914112189686</v>
+        <v>0.0219332707051393</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>0.957380069754925</v>
+        <v>0.966205576551467</v>
       </c>
       <c r="O127" s="3" t="n">
-        <v>0.0109856061404173</v>
+        <v>0.0038148467586396</v>
       </c>
       <c r="P127" s="3" t="n">
-        <v>0.8165214461461739</v>
+        <v>0.726819929386729</v>
       </c>
       <c r="Q127" s="3" t="n">
-        <v>0.0131425034690711</v>
+        <v>0.0201657392710779</v>
       </c>
       <c r="R127" s="3" t="n">
-        <v>0.812391834359065</v>
+        <v>0.815523576283991</v>
       </c>
       <c r="S127" s="3" t="n">
-        <v>0.0290027118494505</v>
+        <v>0.0209036321763732</v>
       </c>
       <c r="T127" s="3" t="n">
-        <v>0.765108416791909</v>
+        <v>0.817390553785924</v>
       </c>
       <c r="U127" s="3" t="n">
-        <v>0.0194424794774026</v>
+        <v>0.0147381558741435</v>
       </c>
       <c r="V127" s="3" t="n">
-        <v>0.8123807948517801</v>
+        <v>0.720095654346591</v>
       </c>
       <c r="W127" s="3" t="n">
-        <v>0.0132902979776578</v>
+        <v>0.0213566030713682</v>
       </c>
       <c r="X127" s="3" t="n">
-        <v>0.471286759999929</v>
+        <v>115.820980559998</v>
       </c>
       <c r="Y127" s="3" t="n">
-        <v>0.0261207558350961</v>
+        <v>0.7742320010681411</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>MC-RBO</t>
+          <t>MC-CCR</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -11046,76 +11046,76 @@
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>0.943014859743122</v>
+        <v>0.941297825561587</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>0.0060782729802797</v>
+        <v>0.004254705742944</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>0.816963448939644</v>
+        <v>0.810894245382203</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>0.0495162286577273</v>
+        <v>0.0322262955758265</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>0.778676901856361</v>
+        <v>0.784763937765943</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>0.0211755166040569</v>
+        <v>0.0183399467826976</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>0.789118309454229</v>
+        <v>0.791327433863679</v>
       </c>
       <c r="K128" s="3" t="n">
-        <v>0.0247476398494972</v>
+        <v>0.0176014841676315</v>
       </c>
       <c r="L128" s="3" t="n">
-        <v>0.483255387815372</v>
+        <v>0.492491106877095</v>
       </c>
       <c r="M128" s="3" t="n">
-        <v>0.141527809485967</v>
+        <v>0.143914112189686</v>
       </c>
       <c r="N128" s="3" t="n">
-        <v>0.95501392229099</v>
+        <v>0.957380069754925</v>
       </c>
       <c r="O128" s="3" t="n">
-        <v>0.0147460009085943</v>
+        <v>0.0109856061404173</v>
       </c>
       <c r="P128" s="3" t="n">
-        <v>0.821498189526995</v>
+        <v>0.8165214461461739</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>0.0195157592420756</v>
+        <v>0.0131425034690711</v>
       </c>
       <c r="R128" s="3" t="n">
-        <v>0.809181465611847</v>
+        <v>0.812391834359065</v>
       </c>
       <c r="S128" s="3" t="n">
-        <v>0.0253516900886223</v>
+        <v>0.0290027118494505</v>
       </c>
       <c r="T128" s="3" t="n">
-        <v>0.759230257508295</v>
+        <v>0.765108416791909</v>
       </c>
       <c r="U128" s="3" t="n">
-        <v>0.0183475694075632</v>
+        <v>0.0194424794774026</v>
       </c>
       <c r="V128" s="3" t="n">
-        <v>0.816408861912281</v>
+        <v>0.8123807948517801</v>
       </c>
       <c r="W128" s="3" t="n">
-        <v>0.019611130806481</v>
+        <v>0.0132902979776578</v>
       </c>
       <c r="X128" s="3" t="n">
-        <v>434.59879974</v>
+        <v>0.471286759999929</v>
       </c>
       <c r="Y128" s="3" t="n">
-        <v>1.88933272596825</v>
+        <v>0.0261207558350961</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>MDO</t>
+          <t>MC-RBO</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -11129,76 +11129,76 @@
         </is>
       </c>
       <c r="D129" s="3" t="n">
-        <v>0.925164305965706</v>
+        <v>0.943014859743122</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>0.007857643432234499</v>
+        <v>0.0060782729802797</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>0.7445946392937191</v>
+        <v>0.816963448939644</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>0.0199315329837249</v>
+        <v>0.0495162286577273</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>0.768590375531886</v>
+        <v>0.778676901856361</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>0.0110283865863002</v>
+        <v>0.0211755166040569</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>0.746238618619479</v>
+        <v>0.789118309454229</v>
       </c>
       <c r="K129" s="3" t="n">
-        <v>0.016211936600519</v>
+        <v>0.0247476398494972</v>
       </c>
       <c r="L129" s="3" t="n">
-        <v>0.411746812597384</v>
+        <v>0.483255387815372</v>
       </c>
       <c r="M129" s="3" t="n">
-        <v>0.0927282706677184</v>
+        <v>0.141527809485967</v>
       </c>
       <c r="N129" s="3" t="n">
-        <v>0.949785396223623</v>
+        <v>0.95501392229099</v>
       </c>
       <c r="O129" s="3" t="n">
-        <v>0.009177169987437299</v>
+        <v>0.0147460009085943</v>
       </c>
       <c r="P129" s="3" t="n">
-        <v>0.774070098447753</v>
+        <v>0.821498189526995</v>
       </c>
       <c r="Q129" s="3" t="n">
-        <v>0.019924448581017</v>
+        <v>0.0195157592420756</v>
       </c>
       <c r="R129" s="3" t="n">
-        <v>0.790408538788053</v>
+        <v>0.809181465611847</v>
       </c>
       <c r="S129" s="3" t="n">
-        <v>0.0254493156034722</v>
+        <v>0.0253516900886223</v>
       </c>
       <c r="T129" s="3" t="n">
-        <v>0.751861222966912</v>
+        <v>0.759230257508295</v>
       </c>
       <c r="U129" s="3" t="n">
-        <v>0.012613403037527</v>
+        <v>0.0183475694075632</v>
       </c>
       <c r="V129" s="3" t="n">
-        <v>0.772184325206664</v>
+        <v>0.816408861912281</v>
       </c>
       <c r="W129" s="3" t="n">
-        <v>0.0196741902387634</v>
+        <v>0.019611130806481</v>
       </c>
       <c r="X129" s="3" t="n">
-        <v>0.734806140000728</v>
+        <v>434.59879974</v>
       </c>
       <c r="Y129" s="3" t="n">
-        <v>0.0187164079003145</v>
+        <v>1.88933272596825</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>NROMM</t>
+          <t>MDO</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -11212,76 +11212,76 @@
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>0.919324739320848</v>
+        <v>0.925164305965706</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>0.0120032833306708</v>
+        <v>0.007857643432234499</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>0.767476481619693</v>
+        <v>0.7445946392937191</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>0.0249137920813382</v>
+        <v>0.0199315329837249</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>0.762745582108991</v>
+        <v>0.768590375531886</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>0.0140403972709062</v>
+        <v>0.0110283865863002</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>0.760938415035015</v>
+        <v>0.746238618619479</v>
       </c>
       <c r="K130" s="3" t="n">
-        <v>0.016199420117075</v>
+        <v>0.016211936600519</v>
       </c>
       <c r="L130" s="3" t="n">
-        <v>0.536767229262257</v>
+        <v>0.411746812597384</v>
       </c>
       <c r="M130" s="3" t="n">
-        <v>0.146476242921394</v>
+        <v>0.0927282706677184</v>
       </c>
       <c r="N130" s="3" t="n">
-        <v>0.960314454367335</v>
+        <v>0.949785396223623</v>
       </c>
       <c r="O130" s="3" t="n">
-        <v>0.0111614432531628</v>
+        <v>0.009177169987437299</v>
       </c>
       <c r="P130" s="3" t="n">
-        <v>0.7568660064661979</v>
+        <v>0.774070098447753</v>
       </c>
       <c r="Q130" s="3" t="n">
-        <v>0.0292445685928635</v>
+        <v>0.019924448581017</v>
       </c>
       <c r="R130" s="3" t="n">
-        <v>0.79387136792476</v>
+        <v>0.790408538788053</v>
       </c>
       <c r="S130" s="3" t="n">
-        <v>0.0228431503504166</v>
+        <v>0.0254493156034722</v>
       </c>
       <c r="T130" s="3" t="n">
-        <v>0.735956495267883</v>
+        <v>0.751861222966912</v>
       </c>
       <c r="U130" s="3" t="n">
-        <v>0.0112646577491649</v>
+        <v>0.012613403037527</v>
       </c>
       <c r="V130" s="3" t="n">
-        <v>0.755479064153314</v>
+        <v>0.772184325206664</v>
       </c>
       <c r="W130" s="3" t="n">
-        <v>0.0286981320081383</v>
+        <v>0.0196741902387634</v>
       </c>
       <c r="X130" s="3" t="n">
-        <v>285.409385199998</v>
+        <v>0.734806140000728</v>
       </c>
       <c r="Y130" s="3" t="n">
-        <v>30.9352936235821</v>
+        <v>0.0187164079003145</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>OREM-M</t>
+          <t>NROMM</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -11295,76 +11295,76 @@
         </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>0.928597195451893</v>
+        <v>0.919324739320848</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>0.0114546859557094</v>
+        <v>0.0120032833306708</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>0.775816039542027</v>
+        <v>0.767476481619693</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>0.039145685391452</v>
+        <v>0.0249137920813382</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>0.7980104102550371</v>
+        <v>0.762745582108991</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>0.0263118924387512</v>
+        <v>0.0140403972709062</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>0.781027209182008</v>
+        <v>0.760938415035015</v>
       </c>
       <c r="K131" s="3" t="n">
-        <v>0.0268332343938942</v>
+        <v>0.016199420117075</v>
       </c>
       <c r="L131" s="3" t="n">
-        <v>0.487501618026457</v>
+        <v>0.536767229262257</v>
       </c>
       <c r="M131" s="3" t="n">
-        <v>0.127516181335003</v>
+        <v>0.146476242921394</v>
       </c>
       <c r="N131" s="3" t="n">
-        <v>0.960305533453826</v>
+        <v>0.960314454367335</v>
       </c>
       <c r="O131" s="3" t="n">
-        <v>0.0077111516536545</v>
+        <v>0.0111614432531628</v>
       </c>
       <c r="P131" s="3" t="n">
-        <v>0.785684193006401</v>
+        <v>0.7568660064661979</v>
       </c>
       <c r="Q131" s="3" t="n">
-        <v>0.0311775100204186</v>
+        <v>0.0292445685928635</v>
       </c>
       <c r="R131" s="3" t="n">
-        <v>0.800755741595092</v>
+        <v>0.79387136792476</v>
       </c>
       <c r="S131" s="3" t="n">
-        <v>0.0198287570548343</v>
+        <v>0.0228431503504166</v>
       </c>
       <c r="T131" s="3" t="n">
-        <v>0.781416442057962</v>
+        <v>0.735956495267883</v>
       </c>
       <c r="U131" s="3" t="n">
-        <v>0.0301939686297051</v>
+        <v>0.0112646577491649</v>
       </c>
       <c r="V131" s="3" t="n">
-        <v>0.784557746827692</v>
+        <v>0.755479064153314</v>
       </c>
       <c r="W131" s="3" t="n">
-        <v>0.0309948690905108</v>
+        <v>0.0286981320081383</v>
       </c>
       <c r="X131" s="3" t="n">
-        <v>1.14699017999955</v>
+        <v>285.409385199998</v>
       </c>
       <c r="Y131" s="3" t="n">
-        <v>0.050622234385949</v>
+        <v>30.9352936235821</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>QC-SMOTE</t>
+          <t>OREM-M</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -11378,76 +11378,76 @@
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>0.940954772388345</v>
+        <v>0.928597195451893</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>0.0053771951469708</v>
+        <v>0.0114546859557094</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>0.802461777012744</v>
+        <v>0.775816039542027</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>0.0370652894561923</v>
+        <v>0.039145685391452</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>0.777162965763017</v>
+        <v>0.7980104102550371</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>0.0280479369815797</v>
+        <v>0.0263118924387512</v>
       </c>
       <c r="J132" s="3" t="n">
-        <v>0.780948591114919</v>
+        <v>0.781027209182008</v>
       </c>
       <c r="K132" s="3" t="n">
-        <v>0.023955249430916</v>
+        <v>0.0268332343938942</v>
       </c>
       <c r="L132" s="3" t="n">
-        <v>0.473412122074128</v>
+        <v>0.487501618026457</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>0.130821414534</v>
+        <v>0.127516181335003</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>0.95293077251374</v>
+        <v>0.960305533453826</v>
       </c>
       <c r="O132" s="3" t="n">
-        <v>0.0127482530531718</v>
+        <v>0.0077111516536545</v>
       </c>
       <c r="P132" s="3" t="n">
-        <v>0.815591171233649</v>
+        <v>0.785684193006401</v>
       </c>
       <c r="Q132" s="3" t="n">
-        <v>0.0175549077437194</v>
+        <v>0.0311775100204186</v>
       </c>
       <c r="R132" s="3" t="n">
-        <v>0.808166306473312</v>
+        <v>0.800755741595092</v>
       </c>
       <c r="S132" s="3" t="n">
-        <v>0.0346471131616302</v>
+        <v>0.0198287570548343</v>
       </c>
       <c r="T132" s="3" t="n">
-        <v>0.759133952928623</v>
+        <v>0.781416442057962</v>
       </c>
       <c r="U132" s="3" t="n">
-        <v>0.0273580934816398</v>
+        <v>0.0301939686297051</v>
       </c>
       <c r="V132" s="3" t="n">
-        <v>0.81078615005244</v>
+        <v>0.784557746827692</v>
       </c>
       <c r="W132" s="3" t="n">
-        <v>0.0184142923193863</v>
+        <v>0.0309948690905108</v>
       </c>
       <c r="X132" s="3" t="n">
-        <v>890.8734626</v>
+        <v>1.14699017999955</v>
       </c>
       <c r="Y132" s="3" t="n">
-        <v>108.561402969</v>
+        <v>0.050622234385949</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>SHSampler</t>
+          <t>QC-SMOTE</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -11461,76 +11461,76 @@
         </is>
       </c>
       <c r="D133" s="3" t="n">
-        <v>0.836250464182773</v>
+        <v>0.940954772388345</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>0.0137583235011002</v>
+        <v>0.0053771951469708</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>0.729856566063214</v>
+        <v>0.802461777012744</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>0.0123441599085809</v>
+        <v>0.0370652894561923</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>0.82160036763722</v>
+        <v>0.777162965763017</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>0.0245276194704117</v>
+        <v>0.0280479369815797</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>0.7531409028398151</v>
+        <v>0.780948591114919</v>
       </c>
       <c r="K133" s="3" t="n">
-        <v>0.013315003857346</v>
+        <v>0.023955249430916</v>
       </c>
       <c r="L133" s="3" t="n">
-        <v>0.7774355616491661</v>
+        <v>0.473412122074128</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>0.0374229595561225</v>
+        <v>0.130821414534</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>0.956857714273616</v>
+        <v>0.95293077251374</v>
       </c>
       <c r="O133" s="3" t="n">
-        <v>0.0060162349116032</v>
+        <v>0.0127482530531718</v>
       </c>
       <c r="P133" s="3" t="n">
-        <v>0.636745403205076</v>
+        <v>0.815591171233649</v>
       </c>
       <c r="Q133" s="3" t="n">
-        <v>0.0257883498697587</v>
+        <v>0.0175549077437194</v>
       </c>
       <c r="R133" s="3" t="n">
-        <v>0.7872558979008411</v>
+        <v>0.808166306473312</v>
       </c>
       <c r="S133" s="3" t="n">
-        <v>0.0187523702257765</v>
+        <v>0.0346471131616302</v>
       </c>
       <c r="T133" s="3" t="n">
-        <v>0.783923748926977</v>
+        <v>0.759133952928623</v>
       </c>
       <c r="U133" s="3" t="n">
-        <v>0.0267918423986459</v>
+        <v>0.0273580934816398</v>
       </c>
       <c r="V133" s="3" t="n">
-        <v>0.6119099711855009</v>
+        <v>0.81078615005244</v>
       </c>
       <c r="W133" s="3" t="n">
-        <v>0.0270968326017769</v>
+        <v>0.0184142923193863</v>
       </c>
       <c r="X133" s="3" t="n">
-        <v>0.358159100000193</v>
+        <v>890.8734626</v>
       </c>
       <c r="Y133" s="3" t="n">
-        <v>0.0123060064997085</v>
+        <v>108.561402969</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>SMOM</t>
+          <t>SHSampler</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -11544,76 +11544,76 @@
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0.916231366377252</v>
+        <v>0.836250464182773</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0.0164308170032864</v>
+        <v>0.0137583235011002</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0.782563847885508</v>
+        <v>0.729856566063214</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0.0323728708498874</v>
+        <v>0.0123441599085809</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0.796526112612733</v>
+        <v>0.82160036763722</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0.0200876119899702</v>
+        <v>0.0245276194704117</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0.785838206974842</v>
+        <v>0.7531409028398151</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0.0251386151835925</v>
+        <v>0.013315003857346</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0.611770493044285</v>
+        <v>0.7774355616491661</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0.126029341308059</v>
+        <v>0.0374229595561225</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0.957419493867615</v>
+        <v>0.956857714273616</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0.0120442481427723</v>
+        <v>0.0060162349116032</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0.756237825909463</v>
+        <v>0.636745403205076</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0.0422217162204128</v>
+        <v>0.0257883498697587</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0.808711520723867</v>
+        <v>0.7872558979008411</v>
       </c>
       <c r="S134" s="3" t="n">
-        <v>0.0258828549639093</v>
+        <v>0.0187523702257765</v>
       </c>
       <c r="T134" s="3" t="n">
-        <v>0.773288606235906</v>
+        <v>0.783923748926977</v>
       </c>
       <c r="U134" s="3" t="n">
-        <v>0.020605207199377</v>
+        <v>0.0267918423986459</v>
       </c>
       <c r="V134" s="3" t="n">
-        <v>0.755218491905098</v>
+        <v>0.6119099711855009</v>
       </c>
       <c r="W134" s="3" t="n">
-        <v>0.0425468947552694</v>
+        <v>0.0270968326017769</v>
       </c>
       <c r="X134" s="3" t="n">
-        <v>902.19075054</v>
+        <v>0.358159100000193</v>
       </c>
       <c r="Y134" s="3" t="n">
-        <v>17.5928445794111</v>
+        <v>0.0123060064997085</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>SOUP</t>
+          <t>SMOM</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -11627,153 +11627,270 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>0.901477132735642</v>
+        <v>0.916231366377252</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>0.009496092146355601</v>
+        <v>0.0164308170032864</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>0.744398590932221</v>
+        <v>0.782563847885508</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>0.0218299863359303</v>
+        <v>0.0323728708498874</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>0.792225582287401</v>
+        <v>0.796526112612733</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>0.0248381781101606</v>
+        <v>0.0200876119899702</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>0.762156429364964</v>
+        <v>0.785838206974842</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>0.0192253323791565</v>
+        <v>0.0251386151835925</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>0.607364147625474</v>
+        <v>0.611770493044285</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>0.131807740862389</v>
+        <v>0.126029341308059</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>0.957246437289012</v>
+        <v>0.957419493867615</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>0.0122036988289502</v>
+        <v>0.0120442481427723</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>0.725335231116767</v>
+        <v>0.756237825909463</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>0.0260677046222215</v>
+        <v>0.0422217162204128</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>0.79448308449505</v>
+        <v>0.808711520723867</v>
       </c>
       <c r="S135" s="3" t="n">
-        <v>0.0308897761777091</v>
+        <v>0.0258828549639093</v>
       </c>
       <c r="T135" s="3" t="n">
-        <v>0.767000626801727</v>
+        <v>0.773288606235906</v>
       </c>
       <c r="U135" s="3" t="n">
-        <v>0.0239335254773585</v>
+        <v>0.020605207199377</v>
       </c>
       <c r="V135" s="3" t="n">
-        <v>0.722905201592552</v>
+        <v>0.755218491905098</v>
       </c>
       <c r="W135" s="3" t="n">
-        <v>0.0260376194790789</v>
+        <v>0.0425468947552694</v>
       </c>
       <c r="X135" s="3" t="n">
-        <v>122.84715602</v>
+        <v>902.19075054</v>
       </c>
       <c r="Y135" s="3" t="n">
-        <v>0.678282578632888</v>
+        <v>17.5928445794111</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
+          <t>SOUP</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>IR30_XJTU</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>0.901477132735642</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>0.009496092146355601</v>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>0.744398590932221</v>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>0.0218299863359303</v>
+      </c>
+      <c r="H136" s="3" t="n">
+        <v>0.792225582287401</v>
+      </c>
+      <c r="I136" s="3" t="n">
+        <v>0.0248381781101606</v>
+      </c>
+      <c r="J136" s="3" t="n">
+        <v>0.762156429364964</v>
+      </c>
+      <c r="K136" s="3" t="n">
+        <v>0.0192253323791565</v>
+      </c>
+      <c r="L136" s="3" t="n">
+        <v>0.607364147625474</v>
+      </c>
+      <c r="M136" s="3" t="n">
+        <v>0.131807740862389</v>
+      </c>
+      <c r="N136" s="3" t="n">
+        <v>0.957246437289012</v>
+      </c>
+      <c r="O136" s="3" t="n">
+        <v>0.0122036988289502</v>
+      </c>
+      <c r="P136" s="3" t="n">
+        <v>0.725335231116767</v>
+      </c>
+      <c r="Q136" s="3" t="n">
+        <v>0.0260677046222215</v>
+      </c>
+      <c r="R136" s="3" t="n">
+        <v>0.79448308449505</v>
+      </c>
+      <c r="S136" s="3" t="n">
+        <v>0.0308897761777091</v>
+      </c>
+      <c r="T136" s="3" t="n">
+        <v>0.767000626801727</v>
+      </c>
+      <c r="U136" s="3" t="n">
+        <v>0.0239335254773585</v>
+      </c>
+      <c r="V136" s="3" t="n">
+        <v>0.722905201592552</v>
+      </c>
+      <c r="W136" s="3" t="n">
+        <v>0.0260376194790789</v>
+      </c>
+      <c r="X136" s="3" t="n">
+        <v>122.84715602</v>
+      </c>
+      <c r="Y136" s="3" t="n">
+        <v>0.678282578632888</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
           <t>SPE</t>
         </is>
       </c>
-      <c r="B136" s="3" t="inlineStr">
+      <c r="B137" s="3" t="inlineStr">
         <is>
           <t>IR30_XJTU</t>
         </is>
       </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="n">
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n">
         <v>0.651897697064007</v>
       </c>
-      <c r="E136" s="3" t="n">
+      <c r="E137" s="3" t="n">
         <v>0.0141973554935903</v>
       </c>
-      <c r="F136" s="3" t="n">
+      <c r="F137" s="3" t="n">
         <v>0.701028095141025</v>
       </c>
-      <c r="G136" s="3" t="n">
+      <c r="G137" s="3" t="n">
         <v>0.018366153861705</v>
       </c>
-      <c r="H136" s="3" t="n">
+      <c r="H137" s="3" t="n">
         <v>0.851754723419059</v>
       </c>
-      <c r="I136" s="3" t="n">
+      <c r="I137" s="3" t="n">
         <v>0.0156530462925217</v>
       </c>
-      <c r="J136" s="3" t="n">
+      <c r="J137" s="3" t="n">
         <v>0.715508191819074</v>
       </c>
-      <c r="K136" s="3" t="n">
+      <c r="K137" s="3" t="n">
         <v>0.0137432683322698</v>
       </c>
-      <c r="L136" s="3" t="n">
+      <c r="L137" s="3" t="n">
         <v>0.835656585239934</v>
       </c>
-      <c r="M136" s="3" t="n">
+      <c r="M137" s="3" t="n">
         <v>0.0155423279532461</v>
       </c>
-      <c r="N136" s="3" t="n">
+      <c r="N137" s="3" t="n">
         <v>0.960963049916538</v>
       </c>
-      <c r="O136" s="3" t="n">
+      <c r="O137" s="3" t="n">
         <v>0.0062096076305159</v>
       </c>
-      <c r="P136" s="3" t="n">
+      <c r="P137" s="3" t="n">
         <v>0.508690039693132</v>
       </c>
-      <c r="Q136" s="3" t="n">
+      <c r="Q137" s="3" t="n">
         <v>0.004061191090878</v>
       </c>
-      <c r="R136" s="3" t="n">
+      <c r="R137" s="3" t="n">
         <v>0.797533864676413</v>
       </c>
-      <c r="S136" s="3" t="n">
+      <c r="S137" s="3" t="n">
         <v>0.0290615469411683</v>
       </c>
-      <c r="T136" s="3" t="n">
+      <c r="T137" s="3" t="n">
         <v>0.819041641509093</v>
       </c>
-      <c r="U136" s="3" t="n">
+      <c r="U137" s="3" t="n">
         <v>0.0229844544780966</v>
       </c>
-      <c r="V136" s="3" t="n">
+      <c r="V137" s="3" t="n">
         <v>0.408767750873879</v>
       </c>
-      <c r="W136" s="3" t="n">
+      <c r="W137" s="3" t="n">
         <v>0.008537641082148001</v>
       </c>
-      <c r="X136" s="3" t="n">
+      <c r="X137" s="3" t="n">
         <v>9.49002206000077</v>
       </c>
-      <c r="Y136" s="3" t="n">
+      <c r="Y137" s="3" t="n">
         <v>0.0584797776019231</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>MC-RBO</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>IR30_Ottawa</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>MC-RBO</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>IR30_Ottawa</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
       </c>
     </row>
   </sheetData>
